--- a/8Bit Computer ver2.0/excel/chips availability.xlsx
+++ b/8Bit Computer ver2.0/excel/chips availability.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home\Desktop\Computer_HTL\8Bit Computer ver2.0\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D051643E-01C4-4695-94AE-8FD2213CDF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15562C8C-67CB-4263-A856-6BB022B2CF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9CC7EE1-7E8B-4FEA-8BE1-446B4A860683}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="239">
   <si>
     <t>Boolean Logic</t>
   </si>
@@ -828,6 +828,18 @@
   </si>
   <si>
     <t>USB C PD Trigger board</t>
+  </si>
+  <si>
+    <t>SN74LVC1GU04</t>
+  </si>
+  <si>
+    <t>1CH Unbuffered</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Not Included</t>
   </si>
 </sst>
 </file>
@@ -1117,13 +1129,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1153,13 +1165,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>324970</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>67236</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>308593</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>19611</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1513,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA67386-7B54-425F-86A0-E9D5FF3EDFA0}">
-  <dimension ref="B1:R127"/>
+  <dimension ref="B1:R128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -1532,17 +1544,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
@@ -1996,106 +2008,110 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="I13" s="3"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>149</v>
+      </c>
       <c r="L13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="N13" s="20" t="s">
+        <v>79</v>
+      </c>
       <c r="O13" s="1"/>
-      <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="2:17" ht="21" x14ac:dyDescent="0.35">
+      <c r="P13" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="D14" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" ht="21" x14ac:dyDescent="0.35">
       <c r="B15" s="1"/>
-      <c r="C15" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>91</v>
-      </c>
+      <c r="D15" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="C16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="7"/>
-      <c r="P16" s="1"/>
+      <c r="C16" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -2104,7 +2120,7 @@
         <v>50</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>64</v>
@@ -2117,8 +2133,8 @@
         <v>7</v>
       </c>
       <c r="I17" s="10"/>
-      <c r="J17" s="7" t="s">
-        <v>19</v>
+      <c r="J17" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>14</v>
@@ -2135,7 +2151,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>64</v>
@@ -2149,10 +2165,10 @@
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L18" s="7"/>
       <c r="M18" s="6"/>
@@ -2162,77 +2178,71 @@
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L19" s="1"/>
-      <c r="N19" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="O19" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="P19" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q19" s="20" t="s">
-        <v>125</v>
-      </c>
+      <c r="F19" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="7"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="7"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
-      <c r="C20" s="16" t="s">
-        <v>138</v>
+      <c r="C20" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G20" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="H20" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="I20" s="18"/>
+        <v>77</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>78</v>
+      </c>
       <c r="J20" s="1" t="s">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c r="L20" s="1"/>
       <c r="N20" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="O20" s="18"/>
+        <v>79</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>80</v>
+      </c>
       <c r="P20" s="25" t="s">
         <v>133</v>
       </c>
@@ -2241,33 +2251,33 @@
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
+      <c r="B21" s="1"/>
       <c r="C21" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="20" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="I21" s="18"/>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="K21" s="1" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="L21" s="1"/>
       <c r="N21" s="20" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O21" s="18"/>
       <c r="P21" s="25" t="s">
@@ -2278,43 +2288,41 @@
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="1"/>
-      <c r="C22" s="23" t="s">
-        <v>50</v>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>139</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I22" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>93</v>
-      </c>
+      <c r="I22" s="18"/>
+      <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="L22" s="1"/>
-      <c r="N22" s="5" t="s">
+      <c r="N22" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="O22" s="21" t="s">
-        <v>80</v>
-      </c>
+      <c r="O22" s="18"/>
       <c r="P22" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="Q22" s="1"/>
+      <c r="Q22" s="20" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
@@ -2322,102 +2330,107 @@
         <v>50</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="N23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="O23" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="P23" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B24" s="1"/>
+      <c r="C24" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K23" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="1"/>
-      <c r="N23" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="O23" s="21"/>
-      <c r="Q23" s="17"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="20" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="I24" s="17"/>
-      <c r="J24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="K24" s="22" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="L24" s="1"/>
       <c r="N24" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="O24" s="21"/>
+      <c r="Q24" s="17"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="17"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="N25" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="O24" s="21"/>
-      <c r="P24" s="25" t="s">
+      <c r="O25" s="21"/>
+      <c r="P25" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="Q24" s="20" t="s">
+      <c r="Q25" s="20" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-      <c r="C25" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="O25" s="6"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
@@ -2425,28 +2438,31 @@
         <v>50</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="10" t="s">
         <v>7</v>
       </c>
       <c r="I26" s="10"/>
-      <c r="J26" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="J26" s="7"/>
       <c r="K26" s="7" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L26" s="7"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="7"/>
+      <c r="M26" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="O26" s="6"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
@@ -2456,24 +2472,24 @@
         <v>50</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G27" s="7"/>
-      <c r="H27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27" s="7"/>
+      <c r="H27" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" s="10"/>
       <c r="J27" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="6"/>
@@ -2483,73 +2499,75 @@
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
-      <c r="C28" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="C28" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I28" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="L28" s="1"/>
-      <c r="N28" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="O28" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="P28" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q28" s="20" t="s">
-        <v>125</v>
-      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="7"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="7"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
-      <c r="C29" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="7"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
+      <c r="C29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="N29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="O29" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="P29" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q29" s="20" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
@@ -2557,7 +2575,7 @@
         <v>50</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>28</v>
@@ -2565,14 +2583,14 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L30" s="7"/>
       <c r="M30" s="6"/>
@@ -2586,25 +2604,25 @@
         <v>50</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>61</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F31" s="7"/>
       <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="H31" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="I31" s="7"/>
-      <c r="J31" s="6"/>
+      <c r="J31" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="K31" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L31" s="7"/>
-      <c r="M31" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="M31" s="6"/>
       <c r="N31" s="7"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -2615,10 +2633,10 @@
         <v>50</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>61</v>
@@ -2626,63 +2644,81 @@
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
+      <c r="J32" s="6"/>
       <c r="K32" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="M32" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="L32" s="7"/>
+      <c r="M32" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="N32" s="7"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C33" s="19" t="s">
+      <c r="B33" s="1"/>
+      <c r="C33" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M33" s="6"/>
+      <c r="N33" s="7"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C34" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="H34" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J34" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K33" s="22" t="s">
+      <c r="K34" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L34" t="s">
         <v>154</v>
       </c>
-      <c r="N33" s="20" t="s">
+      <c r="N34" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="P33" s="25" t="s">
+      <c r="P34" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="Q33" s="20" t="s">
+      <c r="Q34" s="20" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="Q35" s="1"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
@@ -2690,8 +2726,6 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -2723,127 +2757,104 @@
       <c r="L38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="Q39" s="1"/>
+    </row>
+    <row r="40" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="B40" s="1"/>
+      <c r="D40" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="1"/>
-      <c r="C40" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="L40" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="M40" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="N40" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
       <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
-      <c r="C41" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="5" t="s">
+      <c r="C41" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I41" s="5"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="N41" s="5" t="s">
+      <c r="I41" s="11"/>
+      <c r="J41" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="N41" s="11" t="s">
         <v>51</v>
       </c>
       <c r="Q41" s="1"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
-      <c r="C42" s="19" t="s">
-        <v>144</v>
+      <c r="C42" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I42" s="5"/>
-      <c r="J42" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="N42" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P42" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q42" s="5" t="s">
-        <v>125</v>
-      </c>
+      <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
-      <c r="C43" s="23" t="s">
-        <v>50</v>
+      <c r="C43" s="19" t="s">
+        <v>144</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>70</v>
@@ -2857,11 +2868,11 @@
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="1" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="N43" s="5" t="s">
         <v>51</v>
@@ -2874,35 +2885,30 @@
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="1">
-        <v>3</v>
-      </c>
+      <c r="B44" s="1"/>
       <c r="C44" s="23" t="s">
         <v>50</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I44" s="1"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="1" t="s">
         <v>106</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M44" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N44" s="5" t="s">
         <v>51</v>
@@ -2918,17 +2924,17 @@
       <c r="B45" s="1">
         <v>3</v>
       </c>
-      <c r="C45" s="19" t="s">
-        <v>55</v>
+      <c r="C45" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>98</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="5" t="s">
@@ -2936,7 +2942,7 @@
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
@@ -2956,20 +2962,20 @@
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46">
+      <c r="B46" s="1">
         <v>3</v>
       </c>
-      <c r="C46" s="23" t="s">
-        <v>50</v>
+      <c r="C46" s="19" t="s">
+        <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="5" t="s">
@@ -2977,81 +2983,77 @@
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
+      <c r="L46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M46" t="s">
+        <v>105</v>
+      </c>
       <c r="N46" s="5" t="s">
         <v>51</v>
       </c>
+      <c r="P46" s="25" t="s">
+        <v>133</v>
+      </c>
       <c r="Q46" s="5" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="1">
+      <c r="B47">
         <v>3</v>
       </c>
-      <c r="C47" s="19" t="s">
-        <v>55</v>
+      <c r="C47" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>127</v>
-      </c>
+      <c r="G47" s="1"/>
       <c r="H47" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="I47" s="1"/>
       <c r="J47" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>158</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
       <c r="N47" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O47" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="P47" s="25" t="s">
-        <v>133</v>
-      </c>
       <c r="Q47" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="R47" s="5" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B48" s="1">
+        <v>3</v>
+      </c>
       <c r="C48" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G48" s="1"/>
+        <v>121</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="H48" s="5" t="s">
         <v>7</v>
       </c>
@@ -3059,133 +3061,138 @@
         <v>78</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L48" s="1"/>
+        <v>163</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="N48" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O48" s="21" t="s">
+      <c r="O48" s="5" t="s">
         <v>80</v>
       </c>
       <c r="P48" s="25" t="s">
         <v>133</v>
       </c>
       <c r="Q48" s="5" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="R48" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="1">
-        <v>9</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>56</v>
+      <c r="C49" s="19" t="s">
+        <v>55</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H49" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I49" s="5"/>
+      <c r="I49" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="K49" s="1" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="L49" s="1"/>
-      <c r="N49" s="17" t="s">
+      <c r="N49" s="5" t="s">
         <v>51</v>
+      </c>
+      <c r="O49" s="21" t="s">
+        <v>80</v>
       </c>
       <c r="P49" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="Q49" s="17" t="s">
+      <c r="Q49" s="5" t="s">
         <v>125</v>
       </c>
+      <c r="R49" s="5" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B50" s="1"/>
-      <c r="C50" s="19" t="s">
-        <v>131</v>
+      <c r="B50" s="1">
+        <v>9</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="H50" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I50" s="3"/>
-      <c r="J50" s="24" t="s">
-        <v>130</v>
-      </c>
+      <c r="I50" s="5"/>
       <c r="K50" s="1" t="s">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="L50" s="1"/>
-      <c r="N50" s="5" t="s">
+      <c r="N50" s="17" t="s">
         <v>51</v>
       </c>
       <c r="P50" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="Q50" s="5" t="s">
+      <c r="Q50" s="17" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B51" s="1">
-        <v>6</v>
-      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="19" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G51" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="H51" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="24" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="L51" s="24" t="s">
-        <v>172</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="L51" s="1"/>
       <c r="N51" s="5" t="s">
         <v>51</v>
       </c>
@@ -3197,33 +3204,35 @@
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B52" s="1"/>
+      <c r="B52" s="1">
+        <v>6</v>
+      </c>
       <c r="C52" s="19" t="s">
-        <v>176</v>
+        <v>55</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>127</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="G52" s="1"/>
       <c r="H52" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="24" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="L52" s="24"/>
+        <v>171</v>
+      </c>
+      <c r="L52" s="24" t="s">
+        <v>172</v>
+      </c>
       <c r="N52" s="5" t="s">
         <v>51</v>
       </c>
@@ -3240,13 +3249,13 @@
         <v>176</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>178</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>127</v>
@@ -3256,7 +3265,7 @@
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>182</v>
@@ -3272,106 +3281,114 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="D54" s="38" t="s">
+    <row r="54" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B54" s="1"/>
+      <c r="C54" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" s="3"/>
+      <c r="J54" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="L54" s="24"/>
+      <c r="N54" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P54" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="D55" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
-      <c r="L54" s="39"/>
-      <c r="N54" s="1"/>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C55" s="13" t="s">
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="40"/>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C56" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2" t="s">
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2" t="s">
+      <c r="I56" s="2"/>
+      <c r="J56" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="K56" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L55" s="2" t="s">
+      <c r="L56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D56" s="1" t="s">
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="4" t="s">
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I56" s="4"/>
-      <c r="J56" s="1" t="s">
+      <c r="I57" s="4"/>
+      <c r="J57" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="K57" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L56" s="1"/>
-      <c r="N56" s="1"/>
-    </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C57" s="29"/>
-      <c r="D57" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="G57" s="15"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="15"/>
-      <c r="M57" s="29"/>
-      <c r="N57" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="O57" s="29"/>
-      <c r="P57" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q57" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="R57" s="29"/>
+      <c r="L57" s="1"/>
+      <c r="N57" s="1"/>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C58" s="29"/>
       <c r="D58" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F58" s="15" t="s">
         <v>191</v>
@@ -3398,13 +3415,13 @@
     <row r="59" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C59" s="29"/>
       <c r="D59" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="30"/>
@@ -3417,8 +3434,8 @@
         <v>51</v>
       </c>
       <c r="O59" s="29"/>
-      <c r="P59" s="25" t="s">
-        <v>133</v>
+      <c r="P59" s="31" t="s">
+        <v>196</v>
       </c>
       <c r="Q59" s="20" t="s">
         <v>125</v>
@@ -3428,10 +3445,10 @@
     <row r="60" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C60" s="29"/>
       <c r="D60" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F60" s="15" t="s">
         <v>193</v>
@@ -3458,24 +3475,20 @@
     <row r="61" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C61" s="29"/>
       <c r="D61" s="15" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="G61" s="15"/>
       <c r="H61" s="30"/>
       <c r="I61" s="30"/>
       <c r="J61" s="15"/>
-      <c r="K61" s="15">
-        <v>-20</v>
-      </c>
-      <c r="L61" s="15" t="s">
-        <v>206</v>
-      </c>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
       <c r="M61" s="29"/>
       <c r="N61" s="20" t="s">
         <v>51</v>
@@ -3490,22 +3503,26 @@
       <c r="R61" s="29"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C62" s="29" t="s">
-        <v>223</v>
-      </c>
+      <c r="C62" s="29"/>
       <c r="D62" s="15" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="F62" s="15"/>
+        <v>204</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>205</v>
+      </c>
       <c r="G62" s="15"/>
       <c r="H62" s="30"/>
       <c r="I62" s="30"/>
       <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
+      <c r="K62" s="15">
+        <v>-20</v>
+      </c>
+      <c r="L62" s="15" t="s">
+        <v>206</v>
+      </c>
       <c r="M62" s="29"/>
       <c r="N62" s="20" t="s">
         <v>51</v>
@@ -3520,12 +3537,14 @@
       <c r="R62" s="29"/>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C63" s="29"/>
+      <c r="C63" s="29" t="s">
+        <v>223</v>
+      </c>
       <c r="D63" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F63" s="15"/>
       <c r="G63" s="15"/>
@@ -3548,18 +3567,14 @@
       <c r="R63" s="29"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C64" s="29" t="s">
-        <v>229</v>
-      </c>
+      <c r="C64" s="29"/>
       <c r="D64" s="15" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>227</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="F64" s="15"/>
       <c r="G64" s="15"/>
       <c r="H64" s="30"/>
       <c r="I64" s="30"/>
@@ -3580,14 +3595,18 @@
       <c r="R64" s="29"/>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C65" s="29"/>
+      <c r="C65" s="29" t="s">
+        <v>229</v>
+      </c>
       <c r="D65" s="15" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="F65" s="15"/>
+        <v>204</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>227</v>
+      </c>
       <c r="G65" s="15"/>
       <c r="H65" s="30"/>
       <c r="I65" s="30"/>
@@ -3595,27 +3614,41 @@
       <c r="K65" s="15"/>
       <c r="L65" s="15"/>
       <c r="M65" s="29"/>
-      <c r="N65" s="20"/>
+      <c r="N65" s="20" t="s">
+        <v>51</v>
+      </c>
       <c r="O65" s="29"/>
-      <c r="P65" s="40"/>
+      <c r="P65" s="25" t="s">
+        <v>133</v>
+      </c>
       <c r="Q65" s="20" t="s">
         <v>125</v>
       </c>
       <c r="R65" s="29"/>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="32" t="s">
-        <v>195</v>
-      </c>
+      <c r="C66" s="29"/>
+      <c r="D66" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="29"/>
+      <c r="N66" s="20"/>
+      <c r="O66" s="29"/>
+      <c r="P66" s="38"/>
+      <c r="Q66" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="R66" s="29"/>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D67" s="1"/>
@@ -3627,113 +3660,98 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
-    </row>
-    <row r="68" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="D68" s="38" t="s">
+      <c r="M67" s="32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+    </row>
+    <row r="69" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="D69" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="E68" s="39"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="39"/>
-      <c r="J68" s="39"/>
-      <c r="K68" s="39"/>
-      <c r="L68" s="39"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C69" s="11" t="s">
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="40"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="40"/>
+      <c r="K69" s="40"/>
+      <c r="L69" s="40"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C70" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D70" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E70" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F69" s="13" t="s">
+      <c r="F70" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G69" s="13"/>
-      <c r="H69" s="12" t="s">
+      <c r="G70" s="13"/>
+      <c r="H70" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="I69" s="12" t="s">
+      <c r="I70" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="J69" s="11" t="s">
+      <c r="J70" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="K70" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="L69" s="11" t="s">
+      <c r="L70" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="N69" s="13" t="s">
+      <c r="N70" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="O69" s="12" t="s">
+      <c r="O70" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="P69" s="12" t="s">
+      <c r="P70" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="Q69" s="1"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C70" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G70" s="1"/>
-      <c r="H70" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I70" s="3"/>
-      <c r="J70" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K70" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="L70" s="1"/>
-      <c r="N70" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="P70" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q70" s="5" t="s">
-        <v>125</v>
-      </c>
+      <c r="Q70" s="1"/>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C71" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F71" s="33" t="s">
-        <v>209</v>
+        <v>199</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="G71" s="1"/>
-      <c r="H71" s="3"/>
+      <c r="H71" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="I71" s="3"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
+      <c r="J71" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K71" s="22" t="s">
+        <v>171</v>
+      </c>
       <c r="L71" s="1"/>
       <c r="N71" s="5" t="s">
         <v>79</v>
@@ -3750,13 +3768,13 @@
         <v>55</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F72" s="22" t="s">
-        <v>211</v>
+      <c r="F72" s="33" t="s">
+        <v>209</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="3"/>
@@ -3779,13 +3797,13 @@
         <v>55</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F73" s="34" t="s">
-        <v>213</v>
+      <c r="F73" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="3"/>
@@ -3808,13 +3826,13 @@
         <v>55</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F74" s="35" t="s">
-        <v>215</v>
+      <c r="F74" s="34" t="s">
+        <v>213</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="3"/>
@@ -3837,13 +3855,13 @@
         <v>55</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F75" s="36" t="s">
-        <v>217</v>
+      <c r="F75" s="35" t="s">
+        <v>215</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="3"/>
@@ -3862,20 +3880,17 @@
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B76">
-        <v>8</v>
-      </c>
       <c r="C76" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
+      </c>
+      <c r="F76" s="36" t="s">
+        <v>217</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="3"/>
@@ -3883,9 +3898,6 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
-      <c r="M76" t="s">
-        <v>226</v>
-      </c>
       <c r="N76" s="5" t="s">
         <v>79</v>
       </c>
@@ -3897,17 +3909,20 @@
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B77">
+        <v>8</v>
+      </c>
       <c r="C77" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="3"/>
@@ -3915,6 +3930,9 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
+      <c r="M77" t="s">
+        <v>226</v>
+      </c>
       <c r="N77" s="5" t="s">
         <v>79</v>
       </c>
@@ -3926,32 +3944,47 @@
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
+      <c r="C78" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="G78" s="1"/>
-      <c r="H78" s="37"/>
+      <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
-      <c r="N78" s="1"/>
+      <c r="N78" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P78" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q78" s="5" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
-      <c r="H79" s="3"/>
+      <c r="H79" s="37"/>
       <c r="I79" s="3"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
+      <c r="N79" s="1"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C80" s="32" t="s">
-        <v>201</v>
-      </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -3964,7 +3997,7 @@
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C81" s="32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -3977,6 +4010,9 @@
       <c r="L81" s="1"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C82" s="32" t="s">
+        <v>202</v>
+      </c>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -4234,8 +4270,8 @@
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -4482,35 +4518,46 @@
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
     </row>
+    <row r="128" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+      <c r="L128" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="D39:L39"/>
-    <mergeCell ref="D54:L54"/>
-    <mergeCell ref="D14:L14"/>
+    <mergeCell ref="D40:L40"/>
+    <mergeCell ref="D55:L55"/>
+    <mergeCell ref="D15:L15"/>
     <mergeCell ref="D1:L1"/>
-    <mergeCell ref="D68:L68"/>
+    <mergeCell ref="D69:L69"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H16" r:id="rId1" xr:uid="{4C632AA1-6F55-423B-8697-B86F870D7F1B}"/>
-    <hyperlink ref="H17" r:id="rId2" xr:uid="{E6F47877-79D3-493E-A16B-6B7238B0BE31}"/>
-    <hyperlink ref="H56" r:id="rId3" xr:uid="{F47C6505-8196-4511-AE67-D52965EEDE23}"/>
-    <hyperlink ref="H18" r:id="rId4" xr:uid="{E27B66FC-5778-48E1-899B-BB5BB5FBA7E6}"/>
-    <hyperlink ref="H26" r:id="rId5" xr:uid="{C64839DE-A1BA-4157-9A52-801A27FF2915}"/>
-    <hyperlink ref="H22" r:id="rId6" display="Website" xr:uid="{7F6AF889-A9E9-47C4-A2A7-6DBA4D7C81E1}"/>
-    <hyperlink ref="N22" r:id="rId7" display="Datasheet" xr:uid="{CA54F83D-C19B-421F-B1B5-352D51B9919E}"/>
-    <hyperlink ref="N25" r:id="rId8" xr:uid="{33C9152C-4A79-4B03-A18F-588825C5B6B3}"/>
-    <hyperlink ref="N49" r:id="rId9" xr:uid="{0065FA4C-6809-4998-8687-BDB26D400A98}"/>
-    <hyperlink ref="N19" r:id="rId10" display="Datasheet" xr:uid="{26BF3B04-3EC6-47E2-B049-A1546D3BC973}"/>
-    <hyperlink ref="N28" r:id="rId11" display="Datasheet" xr:uid="{C5903ACA-BDB4-47BF-8B56-FF9FBBB36A72}"/>
-    <hyperlink ref="H19" r:id="rId12" display="Website" xr:uid="{F7D68913-EB8F-4945-852A-487A82242546}"/>
-    <hyperlink ref="H25" r:id="rId13" xr:uid="{5663C4BC-2E27-45A8-A9FD-082BBCA9E9F6}"/>
-    <hyperlink ref="H28" r:id="rId14" display="Website" xr:uid="{792E18D9-027D-4AE8-BA75-FC59B1B2CB73}"/>
-    <hyperlink ref="H49" r:id="rId15" xr:uid="{CF9B7135-5770-4CBA-8BB9-3EFCF0F054CE}"/>
-    <hyperlink ref="H41" r:id="rId16" xr:uid="{D6537DC4-6751-4237-9FA6-53AFEFE2BA73}"/>
-    <hyperlink ref="N43" r:id="rId17" xr:uid="{67C9887A-66CC-41B8-9FDB-D1C4BA617492}"/>
-    <hyperlink ref="N41" r:id="rId18" xr:uid="{3FD9C373-E805-4CB8-8CC6-18D15CCA42DF}"/>
-    <hyperlink ref="H43" r:id="rId19" xr:uid="{4EDF24C3-B147-4992-8CEF-2C81201015B8}"/>
+    <hyperlink ref="H17" r:id="rId1" xr:uid="{4C632AA1-6F55-423B-8697-B86F870D7F1B}"/>
+    <hyperlink ref="H18" r:id="rId2" xr:uid="{E6F47877-79D3-493E-A16B-6B7238B0BE31}"/>
+    <hyperlink ref="H57" r:id="rId3" xr:uid="{F47C6505-8196-4511-AE67-D52965EEDE23}"/>
+    <hyperlink ref="H19" r:id="rId4" xr:uid="{E27B66FC-5778-48E1-899B-BB5BB5FBA7E6}"/>
+    <hyperlink ref="H27" r:id="rId5" xr:uid="{C64839DE-A1BA-4157-9A52-801A27FF2915}"/>
+    <hyperlink ref="H23" r:id="rId6" display="Website" xr:uid="{7F6AF889-A9E9-47C4-A2A7-6DBA4D7C81E1}"/>
+    <hyperlink ref="N23" r:id="rId7" display="Datasheet" xr:uid="{CA54F83D-C19B-421F-B1B5-352D51B9919E}"/>
+    <hyperlink ref="N26" r:id="rId8" xr:uid="{33C9152C-4A79-4B03-A18F-588825C5B6B3}"/>
+    <hyperlink ref="N50" r:id="rId9" xr:uid="{0065FA4C-6809-4998-8687-BDB26D400A98}"/>
+    <hyperlink ref="N20" r:id="rId10" display="Datasheet" xr:uid="{26BF3B04-3EC6-47E2-B049-A1546D3BC973}"/>
+    <hyperlink ref="N29" r:id="rId11" display="Datasheet" xr:uid="{C5903ACA-BDB4-47BF-8B56-FF9FBBB36A72}"/>
+    <hyperlink ref="H20" r:id="rId12" display="Website" xr:uid="{F7D68913-EB8F-4945-852A-487A82242546}"/>
+    <hyperlink ref="H26" r:id="rId13" xr:uid="{5663C4BC-2E27-45A8-A9FD-082BBCA9E9F6}"/>
+    <hyperlink ref="H29" r:id="rId14" display="Website" xr:uid="{792E18D9-027D-4AE8-BA75-FC59B1B2CB73}"/>
+    <hyperlink ref="H50" r:id="rId15" xr:uid="{CF9B7135-5770-4CBA-8BB9-3EFCF0F054CE}"/>
+    <hyperlink ref="H42" r:id="rId16" xr:uid="{D6537DC4-6751-4237-9FA6-53AFEFE2BA73}"/>
+    <hyperlink ref="N44" r:id="rId17" xr:uid="{67C9887A-66CC-41B8-9FDB-D1C4BA617492}"/>
+    <hyperlink ref="N42" r:id="rId18" xr:uid="{3FD9C373-E805-4CB8-8CC6-18D15CCA42DF}"/>
+    <hyperlink ref="H44" r:id="rId19" xr:uid="{4EDF24C3-B147-4992-8CEF-2C81201015B8}"/>
     <hyperlink ref="H5" r:id="rId20" xr:uid="{F8A9DA4F-1E4B-4027-89AA-8A8337135A11}"/>
     <hyperlink ref="N5" r:id="rId21" xr:uid="{F5058B02-CCF1-462C-AF78-CFAD9C4A5367}"/>
     <hyperlink ref="H4" r:id="rId22" xr:uid="{AD2CB2AC-934B-40A8-87F0-2DD3411B0BA0}"/>
@@ -4525,15 +4572,15 @@
     <hyperlink ref="N8" r:id="rId31" xr:uid="{85A66E1C-8FFD-404F-AB02-3B2DC717ABCB}"/>
     <hyperlink ref="H6" r:id="rId32" xr:uid="{0B057FC7-5B6C-4B51-8259-E98B5396182B}"/>
     <hyperlink ref="N6" r:id="rId33" xr:uid="{5DE163B5-CB79-4653-B429-7D96467A8E43}"/>
-    <hyperlink ref="I19" r:id="rId34" xr:uid="{EE53776F-D0D2-4515-B316-8D0A9661C7D5}"/>
-    <hyperlink ref="O19" r:id="rId35" xr:uid="{2938CD97-3CFB-4828-B234-DDD6FA51651E}"/>
-    <hyperlink ref="I28" r:id="rId36" xr:uid="{C041C052-5B7F-4797-90DB-07A5A9BD8086}"/>
-    <hyperlink ref="O28" r:id="rId37" xr:uid="{B784EE51-DF03-4479-ABFD-FAE317652025}"/>
-    <hyperlink ref="O22" r:id="rId38" xr:uid="{A63E6F16-81FE-46B5-A1B1-B4BC1F6573F2}"/>
-    <hyperlink ref="I22" r:id="rId39" xr:uid="{220C83A2-FFD8-4402-83E7-F8389CE5032E}"/>
-    <hyperlink ref="H44" r:id="rId40" xr:uid="{C62D8D79-F101-4180-ACFF-0702F492811A}"/>
-    <hyperlink ref="H24" r:id="rId41" display="Website2" xr:uid="{FC620188-EA0A-4DFC-9048-3D95A2D2DBFE}"/>
-    <hyperlink ref="N24" r:id="rId42" xr:uid="{F0F2535F-42C5-4864-82DD-36116DC794C9}"/>
+    <hyperlink ref="I20" r:id="rId34" xr:uid="{EE53776F-D0D2-4515-B316-8D0A9661C7D5}"/>
+    <hyperlink ref="O20" r:id="rId35" xr:uid="{2938CD97-3CFB-4828-B234-DDD6FA51651E}"/>
+    <hyperlink ref="I29" r:id="rId36" xr:uid="{C041C052-5B7F-4797-90DB-07A5A9BD8086}"/>
+    <hyperlink ref="O29" r:id="rId37" xr:uid="{B784EE51-DF03-4479-ABFD-FAE317652025}"/>
+    <hyperlink ref="O23" r:id="rId38" xr:uid="{A63E6F16-81FE-46B5-A1B1-B4BC1F6573F2}"/>
+    <hyperlink ref="I23" r:id="rId39" xr:uid="{220C83A2-FFD8-4402-83E7-F8389CE5032E}"/>
+    <hyperlink ref="H45" r:id="rId40" xr:uid="{C62D8D79-F101-4180-ACFF-0702F492811A}"/>
+    <hyperlink ref="H25" r:id="rId41" display="Website2" xr:uid="{FC620188-EA0A-4DFC-9048-3D95A2D2DBFE}"/>
+    <hyperlink ref="N25" r:id="rId42" xr:uid="{F0F2535F-42C5-4864-82DD-36116DC794C9}"/>
     <hyperlink ref="I5" r:id="rId43" xr:uid="{5D5CF429-1E28-49D6-B19E-03C72E4A0EC4}"/>
     <hyperlink ref="I9" r:id="rId44" xr:uid="{379146E8-AD4E-46D7-A785-14ED81742167}"/>
     <hyperlink ref="I10" r:id="rId45" xr:uid="{025AEAD3-FDD7-4701-B885-935FF1A1F40E}"/>
@@ -4548,8 +4595,8 @@
     <hyperlink ref="O6" r:id="rId54" xr:uid="{2B0393D1-9C98-4B09-843F-3E2A610A923F}"/>
     <hyperlink ref="O7" r:id="rId55" xr:uid="{7230B460-BF16-4B25-9AD0-999DBA80097A}"/>
     <hyperlink ref="O4" r:id="rId56" xr:uid="{677AD2D2-0C13-4EA4-A5A9-72E0106594DE}"/>
-    <hyperlink ref="N46" r:id="rId57" xr:uid="{40A478FC-8924-4710-A43E-370133585A08}"/>
-    <hyperlink ref="H46" r:id="rId58" xr:uid="{891765AC-B469-40EC-813C-5919893FF5BB}"/>
+    <hyperlink ref="N47" r:id="rId57" xr:uid="{40A478FC-8924-4710-A43E-370133585A08}"/>
+    <hyperlink ref="H47" r:id="rId58" xr:uid="{891765AC-B469-40EC-813C-5919893FF5BB}"/>
     <hyperlink ref="Q4" r:id="rId59" xr:uid="{CC3D9E5D-3A0A-43E9-A6FB-ECEAF3E87FBE}"/>
     <hyperlink ref="Q5" r:id="rId60" xr:uid="{3BD4A876-5CA1-4921-BBE4-BB723B41D805}"/>
     <hyperlink ref="Q6" r:id="rId61" xr:uid="{946CB908-8C19-435D-94BA-2ABC09894E34}"/>
@@ -4557,101 +4604,104 @@
     <hyperlink ref="Q8" r:id="rId63" xr:uid="{2F170893-D4B2-43E4-AA17-B3BDB073BDFE}"/>
     <hyperlink ref="Q9" r:id="rId64" xr:uid="{0C53A4D7-BD24-4D99-BD35-01B96FE5E6CD}"/>
     <hyperlink ref="Q10" r:id="rId65" xr:uid="{6DDE68D0-0F25-4356-AE65-5E1262D5C2FD}"/>
-    <hyperlink ref="Q19" r:id="rId66" xr:uid="{10BC4986-0F69-4E48-AE3E-DB047B8561F9}"/>
-    <hyperlink ref="Q28" r:id="rId67" xr:uid="{84B06EEE-62E7-4DD2-B215-B850EFEEBDD5}"/>
-    <hyperlink ref="Q49" r:id="rId68" xr:uid="{DEE65F20-FA5B-4878-889D-BBA69B573B7C}"/>
-    <hyperlink ref="Q24" r:id="rId69" xr:uid="{B024DD3B-1306-4A33-BAB6-DA8CBCF66C81}"/>
-    <hyperlink ref="Q43" r:id="rId70" xr:uid="{BA23315B-529E-4707-9A39-6B3442B6ADFE}"/>
-    <hyperlink ref="Q44" r:id="rId71" xr:uid="{29B13572-2064-4DD1-8E7B-9421C4956652}"/>
-    <hyperlink ref="Q46" r:id="rId72" xr:uid="{35BAA14B-2F9F-4592-AF16-C940162A69F9}"/>
-    <hyperlink ref="N44" r:id="rId73" xr:uid="{63A1230A-6BC9-4382-A381-7EB5E3C505F0}"/>
-    <hyperlink ref="Q48" r:id="rId74" xr:uid="{EBC6B08D-12B4-4976-9AC7-C2395F2D56E6}"/>
-    <hyperlink ref="N48" r:id="rId75" xr:uid="{2C06C958-3C24-46E7-B766-AD20430526C5}"/>
-    <hyperlink ref="H48" r:id="rId76" xr:uid="{DB6CD851-AFD1-4479-B0D4-453D0BFD7FA5}"/>
-    <hyperlink ref="H47" r:id="rId77" xr:uid="{EC464FC1-1A89-4154-9F52-A74B0BFEE481}"/>
-    <hyperlink ref="N47" r:id="rId78" xr:uid="{92B45BB2-CC01-4CB5-9E3E-7D2C4BE24F3E}"/>
-    <hyperlink ref="Q47" r:id="rId79" display="BUY" xr:uid="{60FF01C3-49F8-48A7-8F9E-481F332B29F7}"/>
-    <hyperlink ref="H50" r:id="rId80" xr:uid="{C919B7E8-F2A3-44C6-AAA3-C9AFF9838425}"/>
-    <hyperlink ref="N50" r:id="rId81" xr:uid="{75618C90-808E-40B6-8DA5-E93A774B00F4}"/>
-    <hyperlink ref="Q50" r:id="rId82" xr:uid="{D31F91A2-72C6-4E63-8486-ACC3D5798E3F}"/>
-    <hyperlink ref="H23" r:id="rId83" xr:uid="{B28AB376-A24C-4CE7-96AA-2CA3B384903C}"/>
-    <hyperlink ref="N23" r:id="rId84" xr:uid="{2462CC12-CD75-42B8-B52E-FC208A0C0D00}"/>
-    <hyperlink ref="N45" r:id="rId85" xr:uid="{ADDC0E5E-3350-43F7-970D-90AA6A715DC7}"/>
-    <hyperlink ref="Q45" r:id="rId86" xr:uid="{5F94472F-CA2B-4DB3-8ADB-7E4F7C6EB981}"/>
-    <hyperlink ref="H45" r:id="rId87" location="M29F800FT55N3E2" xr:uid="{799044EA-6D81-4EB5-87E5-41CE14255DBB}"/>
-    <hyperlink ref="H21" r:id="rId88" xr:uid="{B19B548D-587F-4116-A7DB-B2A506DECA30}"/>
-    <hyperlink ref="N21" r:id="rId89" xr:uid="{744CEDEB-72A5-4048-A91C-2A88578DFA95}"/>
-    <hyperlink ref="Q21" r:id="rId90" xr:uid="{479F0893-90B0-4314-9B1D-B67BEEFD8536}"/>
-    <hyperlink ref="H42" r:id="rId91" xr:uid="{AD80FF21-6722-4F90-B04A-2D31DA05E751}"/>
-    <hyperlink ref="N42" r:id="rId92" xr:uid="{D559E430-FAF4-4EE1-8379-890AB8B90EB8}"/>
-    <hyperlink ref="Q42" r:id="rId93" xr:uid="{F6CC58AF-41D1-464C-82A3-1D02E66BCDA1}"/>
+    <hyperlink ref="Q20" r:id="rId66" xr:uid="{10BC4986-0F69-4E48-AE3E-DB047B8561F9}"/>
+    <hyperlink ref="Q29" r:id="rId67" xr:uid="{84B06EEE-62E7-4DD2-B215-B850EFEEBDD5}"/>
+    <hyperlink ref="Q50" r:id="rId68" xr:uid="{DEE65F20-FA5B-4878-889D-BBA69B573B7C}"/>
+    <hyperlink ref="Q25" r:id="rId69" xr:uid="{B024DD3B-1306-4A33-BAB6-DA8CBCF66C81}"/>
+    <hyperlink ref="Q44" r:id="rId70" xr:uid="{BA23315B-529E-4707-9A39-6B3442B6ADFE}"/>
+    <hyperlink ref="Q45" r:id="rId71" xr:uid="{29B13572-2064-4DD1-8E7B-9421C4956652}"/>
+    <hyperlink ref="Q47" r:id="rId72" xr:uid="{35BAA14B-2F9F-4592-AF16-C940162A69F9}"/>
+    <hyperlink ref="N45" r:id="rId73" xr:uid="{63A1230A-6BC9-4382-A381-7EB5E3C505F0}"/>
+    <hyperlink ref="Q49" r:id="rId74" xr:uid="{EBC6B08D-12B4-4976-9AC7-C2395F2D56E6}"/>
+    <hyperlink ref="N49" r:id="rId75" xr:uid="{2C06C958-3C24-46E7-B766-AD20430526C5}"/>
+    <hyperlink ref="H49" r:id="rId76" xr:uid="{DB6CD851-AFD1-4479-B0D4-453D0BFD7FA5}"/>
+    <hyperlink ref="H48" r:id="rId77" xr:uid="{EC464FC1-1A89-4154-9F52-A74B0BFEE481}"/>
+    <hyperlink ref="N48" r:id="rId78" xr:uid="{92B45BB2-CC01-4CB5-9E3E-7D2C4BE24F3E}"/>
+    <hyperlink ref="Q48" r:id="rId79" display="BUY" xr:uid="{60FF01C3-49F8-48A7-8F9E-481F332B29F7}"/>
+    <hyperlink ref="H51" r:id="rId80" xr:uid="{C919B7E8-F2A3-44C6-AAA3-C9AFF9838425}"/>
+    <hyperlink ref="N51" r:id="rId81" xr:uid="{75618C90-808E-40B6-8DA5-E93A774B00F4}"/>
+    <hyperlink ref="Q51" r:id="rId82" xr:uid="{D31F91A2-72C6-4E63-8486-ACC3D5798E3F}"/>
+    <hyperlink ref="H24" r:id="rId83" xr:uid="{B28AB376-A24C-4CE7-96AA-2CA3B384903C}"/>
+    <hyperlink ref="N24" r:id="rId84" xr:uid="{2462CC12-CD75-42B8-B52E-FC208A0C0D00}"/>
+    <hyperlink ref="N46" r:id="rId85" xr:uid="{ADDC0E5E-3350-43F7-970D-90AA6A715DC7}"/>
+    <hyperlink ref="Q46" r:id="rId86" xr:uid="{5F94472F-CA2B-4DB3-8ADB-7E4F7C6EB981}"/>
+    <hyperlink ref="H46" r:id="rId87" location="M29F800FT55N3E2" xr:uid="{799044EA-6D81-4EB5-87E5-41CE14255DBB}"/>
+    <hyperlink ref="H22" r:id="rId88" xr:uid="{B19B548D-587F-4116-A7DB-B2A506DECA30}"/>
+    <hyperlink ref="N22" r:id="rId89" xr:uid="{744CEDEB-72A5-4048-A91C-2A88578DFA95}"/>
+    <hyperlink ref="Q22" r:id="rId90" xr:uid="{479F0893-90B0-4314-9B1D-B67BEEFD8536}"/>
+    <hyperlink ref="H43" r:id="rId91" xr:uid="{AD80FF21-6722-4F90-B04A-2D31DA05E751}"/>
+    <hyperlink ref="N43" r:id="rId92" xr:uid="{D559E430-FAF4-4EE1-8379-890AB8B90EB8}"/>
+    <hyperlink ref="Q43" r:id="rId93" xr:uid="{F6CC58AF-41D1-464C-82A3-1D02E66BCDA1}"/>
     <hyperlink ref="H11" r:id="rId94" xr:uid="{CE72A743-F1DB-4D14-8AD0-EE390C285974}"/>
     <hyperlink ref="N11" r:id="rId95" xr:uid="{C54F2BFB-8DD6-4F25-A830-35475191DC46}"/>
     <hyperlink ref="Q11" r:id="rId96" xr:uid="{B9AAF792-69CB-4E97-A1A5-DF3AD9CDA261}"/>
-    <hyperlink ref="H33" r:id="rId97" xr:uid="{A32FF633-6FAE-4F14-9219-BF1B3A31C39E}"/>
-    <hyperlink ref="N33" r:id="rId98" xr:uid="{C2B3435C-B6C9-4623-96B3-A15699412865}"/>
-    <hyperlink ref="Q33" r:id="rId99" xr:uid="{CA7EDBD9-E87F-465B-92B2-E611A1E8A2F3}"/>
-    <hyperlink ref="I47" r:id="rId100" xr:uid="{80681B69-8466-4DFE-96ED-DB881695E038}"/>
-    <hyperlink ref="O47" r:id="rId101" xr:uid="{1B8723FB-A3B0-4E37-96D5-15DB9C36F4B5}"/>
-    <hyperlink ref="R47" r:id="rId102" xr:uid="{82050D3A-369C-4A89-B315-91B61CF1C78C}"/>
-    <hyperlink ref="I48" r:id="rId103" xr:uid="{E28D4DD1-FCF4-4B5B-B4C1-AFA61830DC34}"/>
-    <hyperlink ref="O48" r:id="rId104" xr:uid="{561E090A-DF6F-4E16-9BBE-4D0C5BFBE235}"/>
-    <hyperlink ref="R48" r:id="rId105" xr:uid="{E490637B-3166-45F4-A700-96DD65491731}"/>
-    <hyperlink ref="H51" r:id="rId106" xr:uid="{6B8DD429-C9B9-47AB-A0C6-54D995A37D94}"/>
-    <hyperlink ref="N51" r:id="rId107" xr:uid="{4E953440-E8A9-4951-87F1-67157569F240}"/>
-    <hyperlink ref="Q51" r:id="rId108" xr:uid="{57B388A3-75E6-488D-BE2B-D9B833BACB45}"/>
+    <hyperlink ref="H34" r:id="rId97" xr:uid="{A32FF633-6FAE-4F14-9219-BF1B3A31C39E}"/>
+    <hyperlink ref="N34" r:id="rId98" xr:uid="{C2B3435C-B6C9-4623-96B3-A15699412865}"/>
+    <hyperlink ref="Q34" r:id="rId99" xr:uid="{CA7EDBD9-E87F-465B-92B2-E611A1E8A2F3}"/>
+    <hyperlink ref="I48" r:id="rId100" xr:uid="{80681B69-8466-4DFE-96ED-DB881695E038}"/>
+    <hyperlink ref="O48" r:id="rId101" xr:uid="{1B8723FB-A3B0-4E37-96D5-15DB9C36F4B5}"/>
+    <hyperlink ref="R48" r:id="rId102" xr:uid="{82050D3A-369C-4A89-B315-91B61CF1C78C}"/>
+    <hyperlink ref="I49" r:id="rId103" xr:uid="{E28D4DD1-FCF4-4B5B-B4C1-AFA61830DC34}"/>
+    <hyperlink ref="O49" r:id="rId104" xr:uid="{561E090A-DF6F-4E16-9BBE-4D0C5BFBE235}"/>
+    <hyperlink ref="R49" r:id="rId105" xr:uid="{E490637B-3166-45F4-A700-96DD65491731}"/>
+    <hyperlink ref="H52" r:id="rId106" xr:uid="{6B8DD429-C9B9-47AB-A0C6-54D995A37D94}"/>
+    <hyperlink ref="N52" r:id="rId107" xr:uid="{4E953440-E8A9-4951-87F1-67157569F240}"/>
+    <hyperlink ref="Q52" r:id="rId108" xr:uid="{57B388A3-75E6-488D-BE2B-D9B833BACB45}"/>
     <hyperlink ref="H12" r:id="rId109" xr:uid="{047AFF56-79C1-4CFD-A099-CD2F20666804}"/>
     <hyperlink ref="N12" r:id="rId110" xr:uid="{C874FFE0-1A9D-4C64-B2D8-2B5B7D864EEF}"/>
     <hyperlink ref="Q12" r:id="rId111" xr:uid="{6D011867-DF84-4464-9649-55AC164A9A2F}"/>
-    <hyperlink ref="H52" r:id="rId112" xr:uid="{9BDE1F0C-97B4-4741-AA2F-BB34E12B2613}"/>
-    <hyperlink ref="H53" r:id="rId113" xr:uid="{778AC8B9-8FAC-41A1-B098-46C3FD08BD5C}"/>
-    <hyperlink ref="N53" r:id="rId114" xr:uid="{4886676B-B4ED-49E5-8DEA-966FE01DE715}"/>
-    <hyperlink ref="N52" r:id="rId115" xr:uid="{3C498D19-AA6F-472C-B98F-A0770D22348E}"/>
-    <hyperlink ref="Q52" r:id="rId116" xr:uid="{48D954F9-FD6B-484C-9C17-8EF77F29EEF8}"/>
-    <hyperlink ref="Q53" r:id="rId117" xr:uid="{C5D0A17F-909E-48E2-89B3-F840B69B21A1}"/>
-    <hyperlink ref="H20" r:id="rId118" xr:uid="{AD74E670-CB67-4CF0-98AC-15C4338CE2CC}"/>
-    <hyperlink ref="N20" r:id="rId119" xr:uid="{809B6A2B-2537-4DC9-98A4-80E23A80D51A}"/>
-    <hyperlink ref="Q20" r:id="rId120" xr:uid="{C3733D1D-43C0-46BC-A557-FB8CD4D39225}"/>
-    <hyperlink ref="N57" r:id="rId121" xr:uid="{52AE5DFF-8AC8-4363-BCB3-94A384C565D8}"/>
-    <hyperlink ref="N58" r:id="rId122" xr:uid="{414C9BCD-7CF7-4DE2-BA57-7DD1AB5A0FD0}"/>
-    <hyperlink ref="Q57" r:id="rId123" xr:uid="{9467689B-EEBC-4374-9E72-3D320D892660}"/>
-    <hyperlink ref="Q58" r:id="rId124" xr:uid="{59C50D68-3822-4E21-8DCB-38B73DCC75C1}"/>
-    <hyperlink ref="N59" r:id="rId125" xr:uid="{B22E3500-96C2-430D-861A-0385FAB0965F}"/>
-    <hyperlink ref="Q59" r:id="rId126" xr:uid="{B032CEA0-7CF2-46B8-BB39-350C01CFC35D}"/>
-    <hyperlink ref="N60" r:id="rId127" xr:uid="{17C049D4-1F98-4448-9BEB-DBA235660298}"/>
-    <hyperlink ref="Q60" r:id="rId128" xr:uid="{93F1B2C3-E2E1-455E-828A-6E20149EE2DD}"/>
-    <hyperlink ref="M66" r:id="rId129" xr:uid="{E6F87D1E-A9C3-4063-BA4B-3C48BDCF3529}"/>
-    <hyperlink ref="H70" r:id="rId130" xr:uid="{1590F363-5B54-413D-92C4-269526397E57}"/>
-    <hyperlink ref="N70" r:id="rId131" xr:uid="{C8E602E0-25DF-4132-90B8-3433782B630C}"/>
-    <hyperlink ref="Q70" r:id="rId132" xr:uid="{15AC358C-0845-4DF6-9B90-0DC741228AEF}"/>
-    <hyperlink ref="C80" r:id="rId133" xr:uid="{DCA814CC-077E-470E-9A6A-680172197756}"/>
-    <hyperlink ref="C81" r:id="rId134" xr:uid="{51A24C82-C0EA-4698-A52E-A029AEDBD4F4}"/>
-    <hyperlink ref="N61" r:id="rId135" xr:uid="{76138DFE-C5A2-4EFC-9B28-2F3C020D3801}"/>
-    <hyperlink ref="Q61" r:id="rId136" xr:uid="{67DA55A1-4D89-4FF1-B17C-42D124B2570E}"/>
-    <hyperlink ref="Q71" r:id="rId137" xr:uid="{9D4382A4-F904-41E1-B435-4589A01E03E7}"/>
-    <hyperlink ref="N71" r:id="rId138" xr:uid="{589B8D49-ECA0-4268-B1FB-46E25B1B7E4E}"/>
-    <hyperlink ref="Q72" r:id="rId139" xr:uid="{49B638E2-302E-4C88-B0CA-66C2B6A9EE1B}"/>
-    <hyperlink ref="N72" r:id="rId140" xr:uid="{D4584256-1E19-4285-97C1-90EC390282C8}"/>
-    <hyperlink ref="N73" r:id="rId141" xr:uid="{4F7DBA63-A996-4741-B44F-BF9C25E975DD}"/>
-    <hyperlink ref="Q73" r:id="rId142" xr:uid="{0CC2B505-39CA-4016-BCA4-146CE6A8EF18}"/>
-    <hyperlink ref="N74" r:id="rId143" display="Datasheet2" xr:uid="{A8A2196D-20AE-4C88-BAA0-0BA9F1547237}"/>
-    <hyperlink ref="Q74" r:id="rId144" xr:uid="{28FD21EE-36C0-40D6-8B88-DF1E2DC0583A}"/>
-    <hyperlink ref="N75" r:id="rId145" display="Datasheet3" xr:uid="{43347140-9AD4-4B38-B219-4FC79534B2AA}"/>
-    <hyperlink ref="Q75" r:id="rId146" xr:uid="{65376778-AD36-4868-A833-D51DD4774842}"/>
-    <hyperlink ref="N76" r:id="rId147" xr:uid="{612638B9-0B1A-472B-9B88-C5DB51EF47F9}"/>
-    <hyperlink ref="Q76" r:id="rId148" xr:uid="{39500D48-B99D-4A43-93E9-00F86FB5ACF4}"/>
-    <hyperlink ref="N62" r:id="rId149" xr:uid="{0329CB29-2EA8-4380-8D4A-DC178B7CD321}"/>
-    <hyperlink ref="Q62" r:id="rId150" xr:uid="{EF372ED3-39E3-49D1-AA0F-93DAD946E71A}"/>
-    <hyperlink ref="N63" r:id="rId151" xr:uid="{AF533AD2-5FE3-4FE6-B9EA-C42D35FC761D}"/>
-    <hyperlink ref="Q63" r:id="rId152" xr:uid="{676B950B-A01E-4215-9B10-DA502C7586DE}"/>
-    <hyperlink ref="Q64" r:id="rId153" xr:uid="{03D6A5FC-D93A-4DCC-A183-323E76CA8110}"/>
-    <hyperlink ref="N64" r:id="rId154" xr:uid="{E5C754CA-97AC-43B4-AA33-09575C56AA6F}"/>
-    <hyperlink ref="N77" r:id="rId155" xr:uid="{8BBD7671-F374-47F0-93CF-6D8F3CF846E4}"/>
-    <hyperlink ref="Q77" r:id="rId156" xr:uid="{FFFDA2AA-98B5-484F-B8A5-3EBCAE9CF1B1}"/>
-    <hyperlink ref="Q65" r:id="rId157" xr:uid="{6F21FB30-BEBA-46C3-9F5F-62E24A3B0E1F}"/>
+    <hyperlink ref="H53" r:id="rId112" xr:uid="{9BDE1F0C-97B4-4741-AA2F-BB34E12B2613}"/>
+    <hyperlink ref="H54" r:id="rId113" xr:uid="{778AC8B9-8FAC-41A1-B098-46C3FD08BD5C}"/>
+    <hyperlink ref="N54" r:id="rId114" xr:uid="{4886676B-B4ED-49E5-8DEA-966FE01DE715}"/>
+    <hyperlink ref="N53" r:id="rId115" xr:uid="{3C498D19-AA6F-472C-B98F-A0770D22348E}"/>
+    <hyperlink ref="Q53" r:id="rId116" xr:uid="{48D954F9-FD6B-484C-9C17-8EF77F29EEF8}"/>
+    <hyperlink ref="Q54" r:id="rId117" xr:uid="{C5D0A17F-909E-48E2-89B3-F840B69B21A1}"/>
+    <hyperlink ref="H21" r:id="rId118" xr:uid="{AD74E670-CB67-4CF0-98AC-15C4338CE2CC}"/>
+    <hyperlink ref="N21" r:id="rId119" xr:uid="{809B6A2B-2537-4DC9-98A4-80E23A80D51A}"/>
+    <hyperlink ref="Q21" r:id="rId120" xr:uid="{C3733D1D-43C0-46BC-A557-FB8CD4D39225}"/>
+    <hyperlink ref="N58" r:id="rId121" xr:uid="{52AE5DFF-8AC8-4363-BCB3-94A384C565D8}"/>
+    <hyperlink ref="N59" r:id="rId122" xr:uid="{414C9BCD-7CF7-4DE2-BA57-7DD1AB5A0FD0}"/>
+    <hyperlink ref="Q58" r:id="rId123" xr:uid="{9467689B-EEBC-4374-9E72-3D320D892660}"/>
+    <hyperlink ref="Q59" r:id="rId124" xr:uid="{59C50D68-3822-4E21-8DCB-38B73DCC75C1}"/>
+    <hyperlink ref="N60" r:id="rId125" xr:uid="{B22E3500-96C2-430D-861A-0385FAB0965F}"/>
+    <hyperlink ref="Q60" r:id="rId126" xr:uid="{B032CEA0-7CF2-46B8-BB39-350C01CFC35D}"/>
+    <hyperlink ref="N61" r:id="rId127" xr:uid="{17C049D4-1F98-4448-9BEB-DBA235660298}"/>
+    <hyperlink ref="Q61" r:id="rId128" xr:uid="{93F1B2C3-E2E1-455E-828A-6E20149EE2DD}"/>
+    <hyperlink ref="M67" r:id="rId129" xr:uid="{E6F87D1E-A9C3-4063-BA4B-3C48BDCF3529}"/>
+    <hyperlink ref="H71" r:id="rId130" xr:uid="{1590F363-5B54-413D-92C4-269526397E57}"/>
+    <hyperlink ref="N71" r:id="rId131" xr:uid="{C8E602E0-25DF-4132-90B8-3433782B630C}"/>
+    <hyperlink ref="Q71" r:id="rId132" xr:uid="{15AC358C-0845-4DF6-9B90-0DC741228AEF}"/>
+    <hyperlink ref="C81" r:id="rId133" xr:uid="{DCA814CC-077E-470E-9A6A-680172197756}"/>
+    <hyperlink ref="C82" r:id="rId134" xr:uid="{51A24C82-C0EA-4698-A52E-A029AEDBD4F4}"/>
+    <hyperlink ref="N62" r:id="rId135" xr:uid="{76138DFE-C5A2-4EFC-9B28-2F3C020D3801}"/>
+    <hyperlink ref="Q62" r:id="rId136" xr:uid="{67DA55A1-4D89-4FF1-B17C-42D124B2570E}"/>
+    <hyperlink ref="Q72" r:id="rId137" xr:uid="{9D4382A4-F904-41E1-B435-4589A01E03E7}"/>
+    <hyperlink ref="N72" r:id="rId138" xr:uid="{589B8D49-ECA0-4268-B1FB-46E25B1B7E4E}"/>
+    <hyperlink ref="Q73" r:id="rId139" xr:uid="{49B638E2-302E-4C88-B0CA-66C2B6A9EE1B}"/>
+    <hyperlink ref="N73" r:id="rId140" xr:uid="{D4584256-1E19-4285-97C1-90EC390282C8}"/>
+    <hyperlink ref="N74" r:id="rId141" xr:uid="{4F7DBA63-A996-4741-B44F-BF9C25E975DD}"/>
+    <hyperlink ref="Q74" r:id="rId142" xr:uid="{0CC2B505-39CA-4016-BCA4-146CE6A8EF18}"/>
+    <hyperlink ref="N75" r:id="rId143" display="Datasheet2" xr:uid="{A8A2196D-20AE-4C88-BAA0-0BA9F1547237}"/>
+    <hyperlink ref="Q75" r:id="rId144" xr:uid="{28FD21EE-36C0-40D6-8B88-DF1E2DC0583A}"/>
+    <hyperlink ref="N76" r:id="rId145" display="Datasheet3" xr:uid="{43347140-9AD4-4B38-B219-4FC79534B2AA}"/>
+    <hyperlink ref="Q76" r:id="rId146" xr:uid="{65376778-AD36-4868-A833-D51DD4774842}"/>
+    <hyperlink ref="N77" r:id="rId147" xr:uid="{612638B9-0B1A-472B-9B88-C5DB51EF47F9}"/>
+    <hyperlink ref="Q77" r:id="rId148" xr:uid="{39500D48-B99D-4A43-93E9-00F86FB5ACF4}"/>
+    <hyperlink ref="N63" r:id="rId149" xr:uid="{0329CB29-2EA8-4380-8D4A-DC178B7CD321}"/>
+    <hyperlink ref="Q63" r:id="rId150" xr:uid="{EF372ED3-39E3-49D1-AA0F-93DAD946E71A}"/>
+    <hyperlink ref="N64" r:id="rId151" xr:uid="{AF533AD2-5FE3-4FE6-B9EA-C42D35FC761D}"/>
+    <hyperlink ref="Q64" r:id="rId152" xr:uid="{676B950B-A01E-4215-9B10-DA502C7586DE}"/>
+    <hyperlink ref="Q65" r:id="rId153" xr:uid="{03D6A5FC-D93A-4DCC-A183-323E76CA8110}"/>
+    <hyperlink ref="N65" r:id="rId154" xr:uid="{E5C754CA-97AC-43B4-AA33-09575C56AA6F}"/>
+    <hyperlink ref="N78" r:id="rId155" xr:uid="{8BBD7671-F374-47F0-93CF-6D8F3CF846E4}"/>
+    <hyperlink ref="Q78" r:id="rId156" xr:uid="{FFFDA2AA-98B5-484F-B8A5-3EBCAE9CF1B1}"/>
+    <hyperlink ref="Q66" r:id="rId157" xr:uid="{6F21FB30-BEBA-46C3-9F5F-62E24A3B0E1F}"/>
+    <hyperlink ref="N13" r:id="rId158" xr:uid="{A48EF5C8-862A-42C5-9C1D-9E8C3C971400}"/>
+    <hyperlink ref="H13" r:id="rId159" xr:uid="{4100AE35-87F2-4D83-8D4C-6FD174A56E28}"/>
+    <hyperlink ref="Q13" r:id="rId160" xr:uid="{2EE2DD77-9D64-4656-A646-71923C9015A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId158"/>
-  <drawing r:id="rId159"/>
+  <pageSetup orientation="portrait" r:id="rId161"/>
+  <drawing r:id="rId162"/>
 </worksheet>
 </file>
--- a/8Bit Computer ver2.0/excel/chips availability.xlsx
+++ b/8Bit Computer ver2.0/excel/chips availability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home\Desktop\Computer_HTL\8Bit Computer ver2.0\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15562C8C-67CB-4263-A856-6BB022B2CF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F46F3B-F2EC-4D53-B3C9-8FA36F66893E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9CC7EE1-7E8B-4FEA-8BE1-446B4A860683}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="248">
   <si>
     <t>Boolean Logic</t>
   </si>
@@ -840,6 +840,33 @@
   </si>
   <si>
     <t>Not Included</t>
+  </si>
+  <si>
+    <t>LM555</t>
+  </si>
+  <si>
+    <t>Timer</t>
+  </si>
+  <si>
+    <t>CMX/NOPB</t>
+  </si>
+  <si>
+    <t>M61P104KT20T607</t>
+  </si>
+  <si>
+    <t>Potentiometer</t>
+  </si>
+  <si>
+    <t>100kOhm</t>
+  </si>
+  <si>
+    <t>TMUX1309DYYR</t>
+  </si>
+  <si>
+    <t>MUX CLKs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">use for clk mux </t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1051,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1136,6 +1163,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1165,13 +1198,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>324970</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>67236</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>308593</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>19611</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1525,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA67386-7B54-425F-86A0-E9D5FF3EDFA0}">
-  <dimension ref="B1:R128"/>
+  <dimension ref="B1:R129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -2720,6 +2753,32 @@
         <v>125</v>
       </c>
     </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C35" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="H35" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="K35" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="N35" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="P35" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q35" s="20" t="s">
+        <v>125</v>
+      </c>
+    </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
       <c r="D36" s="1"/>
@@ -3651,18 +3710,34 @@
       <c r="R66" s="29"/>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="32" t="s">
-        <v>195</v>
-      </c>
+      <c r="C67" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="F67" s="15"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="O67" s="29"/>
+      <c r="P67" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q67" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="R67" s="29"/>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D68" s="1"/>
@@ -3674,113 +3749,98 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
-    </row>
-    <row r="69" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="D69" s="39" t="s">
+      <c r="M68" s="32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+    </row>
+    <row r="70" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="D70" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="E69" s="40"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="40"/>
-      <c r="J69" s="40"/>
-      <c r="K69" s="40"/>
-      <c r="L69" s="40"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C70" s="11" t="s">
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="40"/>
+      <c r="L70" s="40"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C71" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D71" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E71" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F70" s="13" t="s">
+      <c r="F71" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G70" s="13"/>
-      <c r="H70" s="12" t="s">
+      <c r="G71" s="13"/>
+      <c r="H71" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="I71" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J71" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="K71" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="L70" s="11" t="s">
+      <c r="L71" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="N70" s="13" t="s">
+      <c r="N71" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="O70" s="12" t="s">
+      <c r="O71" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="P70" s="12" t="s">
+      <c r="P71" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="Q70" s="1"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C71" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G71" s="1"/>
-      <c r="H71" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I71" s="3"/>
-      <c r="J71" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K71" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="L71" s="1"/>
-      <c r="N71" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="P71" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q71" s="5" t="s">
-        <v>125</v>
-      </c>
+      <c r="Q71" s="1"/>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C72" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F72" s="33" t="s">
-        <v>209</v>
+        <v>199</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="G72" s="1"/>
-      <c r="H72" s="3"/>
+      <c r="H72" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="I72" s="3"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
+      <c r="J72" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K72" s="22" t="s">
+        <v>171</v>
+      </c>
       <c r="L72" s="1"/>
       <c r="N72" s="5" t="s">
         <v>79</v>
@@ -3797,13 +3857,13 @@
         <v>55</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F73" s="22" t="s">
-        <v>211</v>
+      <c r="F73" s="33" t="s">
+        <v>209</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="3"/>
@@ -3826,13 +3886,13 @@
         <v>55</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F74" s="34" t="s">
-        <v>213</v>
+      <c r="F74" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="3"/>
@@ -3855,13 +3915,13 @@
         <v>55</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F75" s="35" t="s">
-        <v>215</v>
+      <c r="F75" s="34" t="s">
+        <v>213</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="3"/>
@@ -3884,13 +3944,13 @@
         <v>55</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="36" t="s">
-        <v>217</v>
+      <c r="F76" s="35" t="s">
+        <v>215</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="3"/>
@@ -3909,20 +3969,17 @@
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B77">
-        <v>8</v>
-      </c>
       <c r="C77" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
+      </c>
+      <c r="F77" s="36" t="s">
+        <v>217</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="3"/>
@@ -3930,9 +3987,6 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
-      <c r="M77" t="s">
-        <v>226</v>
-      </c>
       <c r="N77" s="5" t="s">
         <v>79</v>
       </c>
@@ -3944,17 +3998,20 @@
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B78">
+        <v>8</v>
+      </c>
       <c r="C78" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="3"/>
@@ -3962,6 +4019,9 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
+      <c r="M78" t="s">
+        <v>226</v>
+      </c>
       <c r="N78" s="5" t="s">
         <v>79</v>
       </c>
@@ -3973,32 +4033,64 @@
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
+      <c r="C79" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="G79" s="1"/>
-      <c r="H79" s="37"/>
+      <c r="H79" s="3"/>
       <c r="I79" s="3"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
-      <c r="N79" s="1"/>
+      <c r="N79" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P79" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q79" s="5" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
+      <c r="C80" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="G80" s="1"/>
-      <c r="H80" s="3"/>
+      <c r="H80" s="37"/>
       <c r="I80" s="3"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
+      <c r="N80" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P80" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q80" s="5" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C81" s="32" t="s">
-        <v>201</v>
-      </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -4011,7 +4103,7 @@
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C82" s="32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -4024,6 +4116,9 @@
       <c r="L82" s="1"/>
     </row>
     <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="32" t="s">
+        <v>202</v>
+      </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -4281,8 +4376,8 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -4529,13 +4624,24 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
     </row>
+    <row r="129" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="D15:L15"/>
     <mergeCell ref="D1:L1"/>
-    <mergeCell ref="D69:L69"/>
+    <mergeCell ref="D70:L70"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -4667,41 +4773,48 @@
     <hyperlink ref="Q60" r:id="rId126" xr:uid="{B032CEA0-7CF2-46B8-BB39-350C01CFC35D}"/>
     <hyperlink ref="N61" r:id="rId127" xr:uid="{17C049D4-1F98-4448-9BEB-DBA235660298}"/>
     <hyperlink ref="Q61" r:id="rId128" xr:uid="{93F1B2C3-E2E1-455E-828A-6E20149EE2DD}"/>
-    <hyperlink ref="M67" r:id="rId129" xr:uid="{E6F87D1E-A9C3-4063-BA4B-3C48BDCF3529}"/>
-    <hyperlink ref="H71" r:id="rId130" xr:uid="{1590F363-5B54-413D-92C4-269526397E57}"/>
-    <hyperlink ref="N71" r:id="rId131" xr:uid="{C8E602E0-25DF-4132-90B8-3433782B630C}"/>
-    <hyperlink ref="Q71" r:id="rId132" xr:uid="{15AC358C-0845-4DF6-9B90-0DC741228AEF}"/>
-    <hyperlink ref="C81" r:id="rId133" xr:uid="{DCA814CC-077E-470E-9A6A-680172197756}"/>
-    <hyperlink ref="C82" r:id="rId134" xr:uid="{51A24C82-C0EA-4698-A52E-A029AEDBD4F4}"/>
+    <hyperlink ref="M68" r:id="rId129" xr:uid="{E6F87D1E-A9C3-4063-BA4B-3C48BDCF3529}"/>
+    <hyperlink ref="H72" r:id="rId130" xr:uid="{1590F363-5B54-413D-92C4-269526397E57}"/>
+    <hyperlink ref="N72" r:id="rId131" xr:uid="{C8E602E0-25DF-4132-90B8-3433782B630C}"/>
+    <hyperlink ref="Q72" r:id="rId132" xr:uid="{15AC358C-0845-4DF6-9B90-0DC741228AEF}"/>
+    <hyperlink ref="C82" r:id="rId133" xr:uid="{DCA814CC-077E-470E-9A6A-680172197756}"/>
+    <hyperlink ref="C83" r:id="rId134" xr:uid="{51A24C82-C0EA-4698-A52E-A029AEDBD4F4}"/>
     <hyperlink ref="N62" r:id="rId135" xr:uid="{76138DFE-C5A2-4EFC-9B28-2F3C020D3801}"/>
     <hyperlink ref="Q62" r:id="rId136" xr:uid="{67DA55A1-4D89-4FF1-B17C-42D124B2570E}"/>
-    <hyperlink ref="Q72" r:id="rId137" xr:uid="{9D4382A4-F904-41E1-B435-4589A01E03E7}"/>
-    <hyperlink ref="N72" r:id="rId138" xr:uid="{589B8D49-ECA0-4268-B1FB-46E25B1B7E4E}"/>
-    <hyperlink ref="Q73" r:id="rId139" xr:uid="{49B638E2-302E-4C88-B0CA-66C2B6A9EE1B}"/>
-    <hyperlink ref="N73" r:id="rId140" xr:uid="{D4584256-1E19-4285-97C1-90EC390282C8}"/>
-    <hyperlink ref="N74" r:id="rId141" xr:uid="{4F7DBA63-A996-4741-B44F-BF9C25E975DD}"/>
-    <hyperlink ref="Q74" r:id="rId142" xr:uid="{0CC2B505-39CA-4016-BCA4-146CE6A8EF18}"/>
-    <hyperlink ref="N75" r:id="rId143" display="Datasheet2" xr:uid="{A8A2196D-20AE-4C88-BAA0-0BA9F1547237}"/>
-    <hyperlink ref="Q75" r:id="rId144" xr:uid="{28FD21EE-36C0-40D6-8B88-DF1E2DC0583A}"/>
-    <hyperlink ref="N76" r:id="rId145" display="Datasheet3" xr:uid="{43347140-9AD4-4B38-B219-4FC79534B2AA}"/>
-    <hyperlink ref="Q76" r:id="rId146" xr:uid="{65376778-AD36-4868-A833-D51DD4774842}"/>
-    <hyperlink ref="N77" r:id="rId147" xr:uid="{612638B9-0B1A-472B-9B88-C5DB51EF47F9}"/>
-    <hyperlink ref="Q77" r:id="rId148" xr:uid="{39500D48-B99D-4A43-93E9-00F86FB5ACF4}"/>
+    <hyperlink ref="Q73" r:id="rId137" xr:uid="{9D4382A4-F904-41E1-B435-4589A01E03E7}"/>
+    <hyperlink ref="N73" r:id="rId138" xr:uid="{589B8D49-ECA0-4268-B1FB-46E25B1B7E4E}"/>
+    <hyperlink ref="Q74" r:id="rId139" xr:uid="{49B638E2-302E-4C88-B0CA-66C2B6A9EE1B}"/>
+    <hyperlink ref="N74" r:id="rId140" xr:uid="{D4584256-1E19-4285-97C1-90EC390282C8}"/>
+    <hyperlink ref="N75" r:id="rId141" xr:uid="{4F7DBA63-A996-4741-B44F-BF9C25E975DD}"/>
+    <hyperlink ref="Q75" r:id="rId142" xr:uid="{0CC2B505-39CA-4016-BCA4-146CE6A8EF18}"/>
+    <hyperlink ref="N76" r:id="rId143" display="Datasheet2" xr:uid="{A8A2196D-20AE-4C88-BAA0-0BA9F1547237}"/>
+    <hyperlink ref="Q76" r:id="rId144" xr:uid="{28FD21EE-36C0-40D6-8B88-DF1E2DC0583A}"/>
+    <hyperlink ref="N77" r:id="rId145" display="Datasheet3" xr:uid="{43347140-9AD4-4B38-B219-4FC79534B2AA}"/>
+    <hyperlink ref="Q77" r:id="rId146" xr:uid="{65376778-AD36-4868-A833-D51DD4774842}"/>
+    <hyperlink ref="N78" r:id="rId147" xr:uid="{612638B9-0B1A-472B-9B88-C5DB51EF47F9}"/>
+    <hyperlink ref="Q78" r:id="rId148" xr:uid="{39500D48-B99D-4A43-93E9-00F86FB5ACF4}"/>
     <hyperlink ref="N63" r:id="rId149" xr:uid="{0329CB29-2EA8-4380-8D4A-DC178B7CD321}"/>
     <hyperlink ref="Q63" r:id="rId150" xr:uid="{EF372ED3-39E3-49D1-AA0F-93DAD946E71A}"/>
     <hyperlink ref="N64" r:id="rId151" xr:uid="{AF533AD2-5FE3-4FE6-B9EA-C42D35FC761D}"/>
     <hyperlink ref="Q64" r:id="rId152" xr:uid="{676B950B-A01E-4215-9B10-DA502C7586DE}"/>
     <hyperlink ref="Q65" r:id="rId153" xr:uid="{03D6A5FC-D93A-4DCC-A183-323E76CA8110}"/>
     <hyperlink ref="N65" r:id="rId154" xr:uid="{E5C754CA-97AC-43B4-AA33-09575C56AA6F}"/>
-    <hyperlink ref="N78" r:id="rId155" xr:uid="{8BBD7671-F374-47F0-93CF-6D8F3CF846E4}"/>
-    <hyperlink ref="Q78" r:id="rId156" xr:uid="{FFFDA2AA-98B5-484F-B8A5-3EBCAE9CF1B1}"/>
+    <hyperlink ref="N79" r:id="rId155" xr:uid="{8BBD7671-F374-47F0-93CF-6D8F3CF846E4}"/>
+    <hyperlink ref="Q79" r:id="rId156" xr:uid="{FFFDA2AA-98B5-484F-B8A5-3EBCAE9CF1B1}"/>
     <hyperlink ref="Q66" r:id="rId157" xr:uid="{6F21FB30-BEBA-46C3-9F5F-62E24A3B0E1F}"/>
     <hyperlink ref="N13" r:id="rId158" xr:uid="{A48EF5C8-862A-42C5-9C1D-9E8C3C971400}"/>
     <hyperlink ref="H13" r:id="rId159" xr:uid="{4100AE35-87F2-4D83-8D4C-6FD174A56E28}"/>
     <hyperlink ref="Q13" r:id="rId160" xr:uid="{2EE2DD77-9D64-4656-A646-71923C9015A7}"/>
+    <hyperlink ref="Q35" r:id="rId161" xr:uid="{49C123B4-AE83-492D-967C-32D38ABC6711}"/>
+    <hyperlink ref="N35" r:id="rId162" xr:uid="{34598773-63FA-496F-835F-2287A7B73125}"/>
+    <hyperlink ref="H35" r:id="rId163" xr:uid="{FB34A553-DE5D-49F2-B8FB-56E2AFBF2482}"/>
+    <hyperlink ref="N80" r:id="rId164" xr:uid="{B5FA9E12-05AE-43F0-BB1F-A27FD0A8B2B8}"/>
+    <hyperlink ref="Q80" r:id="rId165" xr:uid="{14B71C3C-31AE-4335-9667-E458C0144A4C}"/>
+    <hyperlink ref="N67" r:id="rId166" xr:uid="{3AE51AD7-8098-4571-8953-1161DA5B67C6}"/>
+    <hyperlink ref="Q67" r:id="rId167" xr:uid="{FB93DBF4-4711-4390-B014-9F008CAD1EA2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId161"/>
-  <drawing r:id="rId162"/>
+  <pageSetup orientation="portrait" r:id="rId168"/>
+  <drawing r:id="rId169"/>
 </worksheet>
 </file>
--- a/8Bit Computer ver2.0/excel/chips availability.xlsx
+++ b/8Bit Computer ver2.0/excel/chips availability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home\Desktop\Computer_HTL\8Bit Computer ver2.0\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F46F3B-F2EC-4D53-B3C9-8FA36F66893E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967F6007-B5AD-420D-ABEC-138A5DFC9508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9CC7EE1-7E8B-4FEA-8BE1-446B4A860683}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="252">
   <si>
     <t>Boolean Logic</t>
   </si>
@@ -867,6 +867,18 @@
   </si>
   <si>
     <t xml:space="preserve">use for clk mux </t>
+  </si>
+  <si>
+    <t>use4</t>
+  </si>
+  <si>
+    <t>1N4148WS-7-F</t>
+  </si>
+  <si>
+    <t>diode</t>
+  </si>
+  <si>
+    <t>0.086</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1063,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1157,16 +1169,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1198,13 +1207,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>324970</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>67236</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>308593</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>19611</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1558,7 +1567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA67386-7B54-425F-86A0-E9D5FF3EDFA0}">
-  <dimension ref="B1:R129"/>
+  <dimension ref="B1:R130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -1577,17 +1586,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
@@ -2091,17 +2100,17 @@
     </row>
     <row r="15" spans="2:17" ht="21" x14ac:dyDescent="0.35">
       <c r="B15" s="1"/>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="Q15" s="1"/>
@@ -2763,10 +2772,10 @@
       <c r="E35" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="H35" s="42" t="s">
+      <c r="H35" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="K35" s="41" t="s">
+      <c r="K35" s="22" t="s">
         <v>241</v>
       </c>
       <c r="N35" s="20" t="s">
@@ -2831,17 +2840,17 @@
     </row>
     <row r="40" spans="2:18" ht="21" x14ac:dyDescent="0.35">
       <c r="B40" s="1"/>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
+      <c r="K40" s="41"/>
+      <c r="L40" s="41"/>
       <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
@@ -3379,17 +3388,17 @@
       </c>
     </row>
     <row r="55" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="D55" s="39" t="s">
+      <c r="D55" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
-      <c r="L55" s="40"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41"/>
+      <c r="L55" s="41"/>
       <c r="N55" s="1"/>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.25">
@@ -3740,18 +3749,36 @@
       <c r="R67" s="29"/>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="32" t="s">
-        <v>195</v>
-      </c>
+      <c r="C68" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="F68" s="15"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="O68" s="29"/>
+      <c r="P68" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q68" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="R68" s="29"/>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D69" s="1"/>
@@ -3763,113 +3790,98 @@
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
-    </row>
-    <row r="70" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="D70" s="39" t="s">
+      <c r="M69" s="32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+    </row>
+    <row r="71" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="D71" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="40"/>
-      <c r="J70" s="40"/>
-      <c r="K70" s="40"/>
-      <c r="L70" s="40"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C71" s="11" t="s">
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
+      <c r="J71" s="41"/>
+      <c r="K71" s="41"/>
+      <c r="L71" s="41"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C72" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D72" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E72" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F71" s="13" t="s">
+      <c r="F72" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G71" s="13"/>
-      <c r="H71" s="12" t="s">
+      <c r="G72" s="13"/>
+      <c r="H72" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="I71" s="12" t="s">
+      <c r="I72" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="J72" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="K72" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="L71" s="11" t="s">
+      <c r="L72" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="N71" s="13" t="s">
+      <c r="N72" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="O71" s="12" t="s">
+      <c r="O72" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="P71" s="12" t="s">
+      <c r="P72" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="Q71" s="1"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C72" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G72" s="1"/>
-      <c r="H72" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I72" s="3"/>
-      <c r="J72" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K72" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="L72" s="1"/>
-      <c r="N72" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="P72" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q72" s="5" t="s">
-        <v>125</v>
-      </c>
+      <c r="Q72" s="1"/>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C73" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F73" s="33" t="s">
-        <v>209</v>
+        <v>199</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="G73" s="1"/>
-      <c r="H73" s="3"/>
+      <c r="H73" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="I73" s="3"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
+      <c r="J73" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K73" s="22" t="s">
+        <v>171</v>
+      </c>
       <c r="L73" s="1"/>
       <c r="N73" s="5" t="s">
         <v>79</v>
@@ -3886,13 +3898,13 @@
         <v>55</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F74" s="22" t="s">
-        <v>211</v>
+      <c r="F74" s="33" t="s">
+        <v>209</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="3"/>
@@ -3915,13 +3927,13 @@
         <v>55</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F75" s="34" t="s">
-        <v>213</v>
+      <c r="F75" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="3"/>
@@ -3944,13 +3956,13 @@
         <v>55</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="35" t="s">
-        <v>215</v>
+      <c r="F76" s="34" t="s">
+        <v>213</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="3"/>
@@ -3973,13 +3985,13 @@
         <v>55</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F77" s="36" t="s">
-        <v>217</v>
+      <c r="F77" s="35" t="s">
+        <v>215</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="3"/>
@@ -3998,20 +4010,17 @@
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B78">
-        <v>8</v>
-      </c>
       <c r="C78" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
+      </c>
+      <c r="F78" s="36" t="s">
+        <v>217</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="3"/>
@@ -4019,9 +4028,6 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
-      <c r="M78" t="s">
-        <v>226</v>
-      </c>
       <c r="N78" s="5" t="s">
         <v>79</v>
       </c>
@@ -4033,17 +4039,20 @@
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B79">
+        <v>8</v>
+      </c>
       <c r="C79" s="19" t="s">
         <v>55</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="3"/>
@@ -4051,6 +4060,9 @@
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
+      <c r="M79" t="s">
+        <v>226</v>
+      </c>
       <c r="N79" s="5" t="s">
         <v>79</v>
       </c>
@@ -4066,16 +4078,16 @@
         <v>55</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G80" s="1"/>
-      <c r="H80" s="37"/>
+      <c r="H80" s="3"/>
       <c r="I80" s="3"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -4090,21 +4102,36 @@
         <v>125</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C81" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="G81" s="1"/>
-      <c r="H81" s="3"/>
+      <c r="H81" s="37"/>
       <c r="I81" s="3"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C82" s="32" t="s">
-        <v>201</v>
-      </c>
+      <c r="N81" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P81" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q81" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -4115,9 +4142,9 @@
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
     </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -4129,7 +4156,10 @@
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C84" s="32" t="s">
+        <v>202</v>
+      </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
@@ -4140,7 +4170,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
     </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -4151,7 +4181,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
     </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
@@ -4162,7 +4192,7 @@
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
     </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -4173,7 +4203,7 @@
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
     </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -4184,7 +4214,7 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
     </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
@@ -4195,7 +4225,7 @@
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
@@ -4206,7 +4236,7 @@
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
     </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
@@ -4217,7 +4247,7 @@
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
@@ -4228,7 +4258,7 @@
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
     </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -4239,7 +4269,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
     </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -4250,7 +4280,7 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
@@ -4261,7 +4291,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -4387,8 +4417,8 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -4635,13 +4665,24 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
     </row>
+    <row r="130" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+      <c r="L130" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="D15:L15"/>
     <mergeCell ref="D1:L1"/>
-    <mergeCell ref="D70:L70"/>
+    <mergeCell ref="D71:L71"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
@@ -4773,34 +4814,34 @@
     <hyperlink ref="Q60" r:id="rId126" xr:uid="{B032CEA0-7CF2-46B8-BB39-350C01CFC35D}"/>
     <hyperlink ref="N61" r:id="rId127" xr:uid="{17C049D4-1F98-4448-9BEB-DBA235660298}"/>
     <hyperlink ref="Q61" r:id="rId128" xr:uid="{93F1B2C3-E2E1-455E-828A-6E20149EE2DD}"/>
-    <hyperlink ref="M68" r:id="rId129" xr:uid="{E6F87D1E-A9C3-4063-BA4B-3C48BDCF3529}"/>
-    <hyperlink ref="H72" r:id="rId130" xr:uid="{1590F363-5B54-413D-92C4-269526397E57}"/>
-    <hyperlink ref="N72" r:id="rId131" xr:uid="{C8E602E0-25DF-4132-90B8-3433782B630C}"/>
-    <hyperlink ref="Q72" r:id="rId132" xr:uid="{15AC358C-0845-4DF6-9B90-0DC741228AEF}"/>
-    <hyperlink ref="C82" r:id="rId133" xr:uid="{DCA814CC-077E-470E-9A6A-680172197756}"/>
-    <hyperlink ref="C83" r:id="rId134" xr:uid="{51A24C82-C0EA-4698-A52E-A029AEDBD4F4}"/>
+    <hyperlink ref="M69" r:id="rId129" xr:uid="{E6F87D1E-A9C3-4063-BA4B-3C48BDCF3529}"/>
+    <hyperlink ref="H73" r:id="rId130" xr:uid="{1590F363-5B54-413D-92C4-269526397E57}"/>
+    <hyperlink ref="N73" r:id="rId131" xr:uid="{C8E602E0-25DF-4132-90B8-3433782B630C}"/>
+    <hyperlink ref="Q73" r:id="rId132" xr:uid="{15AC358C-0845-4DF6-9B90-0DC741228AEF}"/>
+    <hyperlink ref="C83" r:id="rId133" xr:uid="{DCA814CC-077E-470E-9A6A-680172197756}"/>
+    <hyperlink ref="C84" r:id="rId134" xr:uid="{51A24C82-C0EA-4698-A52E-A029AEDBD4F4}"/>
     <hyperlink ref="N62" r:id="rId135" xr:uid="{76138DFE-C5A2-4EFC-9B28-2F3C020D3801}"/>
     <hyperlink ref="Q62" r:id="rId136" xr:uid="{67DA55A1-4D89-4FF1-B17C-42D124B2570E}"/>
-    <hyperlink ref="Q73" r:id="rId137" xr:uid="{9D4382A4-F904-41E1-B435-4589A01E03E7}"/>
-    <hyperlink ref="N73" r:id="rId138" xr:uid="{589B8D49-ECA0-4268-B1FB-46E25B1B7E4E}"/>
-    <hyperlink ref="Q74" r:id="rId139" xr:uid="{49B638E2-302E-4C88-B0CA-66C2B6A9EE1B}"/>
-    <hyperlink ref="N74" r:id="rId140" xr:uid="{D4584256-1E19-4285-97C1-90EC390282C8}"/>
-    <hyperlink ref="N75" r:id="rId141" xr:uid="{4F7DBA63-A996-4741-B44F-BF9C25E975DD}"/>
-    <hyperlink ref="Q75" r:id="rId142" xr:uid="{0CC2B505-39CA-4016-BCA4-146CE6A8EF18}"/>
-    <hyperlink ref="N76" r:id="rId143" display="Datasheet2" xr:uid="{A8A2196D-20AE-4C88-BAA0-0BA9F1547237}"/>
-    <hyperlink ref="Q76" r:id="rId144" xr:uid="{28FD21EE-36C0-40D6-8B88-DF1E2DC0583A}"/>
-    <hyperlink ref="N77" r:id="rId145" display="Datasheet3" xr:uid="{43347140-9AD4-4B38-B219-4FC79534B2AA}"/>
-    <hyperlink ref="Q77" r:id="rId146" xr:uid="{65376778-AD36-4868-A833-D51DD4774842}"/>
-    <hyperlink ref="N78" r:id="rId147" xr:uid="{612638B9-0B1A-472B-9B88-C5DB51EF47F9}"/>
-    <hyperlink ref="Q78" r:id="rId148" xr:uid="{39500D48-B99D-4A43-93E9-00F86FB5ACF4}"/>
+    <hyperlink ref="Q74" r:id="rId137" xr:uid="{9D4382A4-F904-41E1-B435-4589A01E03E7}"/>
+    <hyperlink ref="N74" r:id="rId138" xr:uid="{589B8D49-ECA0-4268-B1FB-46E25B1B7E4E}"/>
+    <hyperlink ref="Q75" r:id="rId139" xr:uid="{49B638E2-302E-4C88-B0CA-66C2B6A9EE1B}"/>
+    <hyperlink ref="N75" r:id="rId140" xr:uid="{D4584256-1E19-4285-97C1-90EC390282C8}"/>
+    <hyperlink ref="N76" r:id="rId141" xr:uid="{4F7DBA63-A996-4741-B44F-BF9C25E975DD}"/>
+    <hyperlink ref="Q76" r:id="rId142" xr:uid="{0CC2B505-39CA-4016-BCA4-146CE6A8EF18}"/>
+    <hyperlink ref="N77" r:id="rId143" display="Datasheet2" xr:uid="{A8A2196D-20AE-4C88-BAA0-0BA9F1547237}"/>
+    <hyperlink ref="Q77" r:id="rId144" xr:uid="{28FD21EE-36C0-40D6-8B88-DF1E2DC0583A}"/>
+    <hyperlink ref="N78" r:id="rId145" display="Datasheet3" xr:uid="{43347140-9AD4-4B38-B219-4FC79534B2AA}"/>
+    <hyperlink ref="Q78" r:id="rId146" xr:uid="{65376778-AD36-4868-A833-D51DD4774842}"/>
+    <hyperlink ref="N79" r:id="rId147" xr:uid="{612638B9-0B1A-472B-9B88-C5DB51EF47F9}"/>
+    <hyperlink ref="Q79" r:id="rId148" xr:uid="{39500D48-B99D-4A43-93E9-00F86FB5ACF4}"/>
     <hyperlink ref="N63" r:id="rId149" xr:uid="{0329CB29-2EA8-4380-8D4A-DC178B7CD321}"/>
     <hyperlink ref="Q63" r:id="rId150" xr:uid="{EF372ED3-39E3-49D1-AA0F-93DAD946E71A}"/>
     <hyperlink ref="N64" r:id="rId151" xr:uid="{AF533AD2-5FE3-4FE6-B9EA-C42D35FC761D}"/>
     <hyperlink ref="Q64" r:id="rId152" xr:uid="{676B950B-A01E-4215-9B10-DA502C7586DE}"/>
     <hyperlink ref="Q65" r:id="rId153" xr:uid="{03D6A5FC-D93A-4DCC-A183-323E76CA8110}"/>
     <hyperlink ref="N65" r:id="rId154" xr:uid="{E5C754CA-97AC-43B4-AA33-09575C56AA6F}"/>
-    <hyperlink ref="N79" r:id="rId155" xr:uid="{8BBD7671-F374-47F0-93CF-6D8F3CF846E4}"/>
-    <hyperlink ref="Q79" r:id="rId156" xr:uid="{FFFDA2AA-98B5-484F-B8A5-3EBCAE9CF1B1}"/>
+    <hyperlink ref="N80" r:id="rId155" xr:uid="{8BBD7671-F374-47F0-93CF-6D8F3CF846E4}"/>
+    <hyperlink ref="Q80" r:id="rId156" xr:uid="{FFFDA2AA-98B5-484F-B8A5-3EBCAE9CF1B1}"/>
     <hyperlink ref="Q66" r:id="rId157" xr:uid="{6F21FB30-BEBA-46C3-9F5F-62E24A3B0E1F}"/>
     <hyperlink ref="N13" r:id="rId158" xr:uid="{A48EF5C8-862A-42C5-9C1D-9E8C3C971400}"/>
     <hyperlink ref="H13" r:id="rId159" xr:uid="{4100AE35-87F2-4D83-8D4C-6FD174A56E28}"/>
@@ -4808,13 +4849,15 @@
     <hyperlink ref="Q35" r:id="rId161" xr:uid="{49C123B4-AE83-492D-967C-32D38ABC6711}"/>
     <hyperlink ref="N35" r:id="rId162" xr:uid="{34598773-63FA-496F-835F-2287A7B73125}"/>
     <hyperlink ref="H35" r:id="rId163" xr:uid="{FB34A553-DE5D-49F2-B8FB-56E2AFBF2482}"/>
-    <hyperlink ref="N80" r:id="rId164" xr:uid="{B5FA9E12-05AE-43F0-BB1F-A27FD0A8B2B8}"/>
-    <hyperlink ref="Q80" r:id="rId165" xr:uid="{14B71C3C-31AE-4335-9667-E458C0144A4C}"/>
+    <hyperlink ref="N81" r:id="rId164" xr:uid="{B5FA9E12-05AE-43F0-BB1F-A27FD0A8B2B8}"/>
+    <hyperlink ref="Q81" r:id="rId165" xr:uid="{14B71C3C-31AE-4335-9667-E458C0144A4C}"/>
     <hyperlink ref="N67" r:id="rId166" xr:uid="{3AE51AD7-8098-4571-8953-1161DA5B67C6}"/>
     <hyperlink ref="Q67" r:id="rId167" xr:uid="{FB93DBF4-4711-4390-B014-9F008CAD1EA2}"/>
+    <hyperlink ref="N68" r:id="rId168" xr:uid="{423BC78F-9BC2-4E5D-8B46-651508C47445}"/>
+    <hyperlink ref="Q68" r:id="rId169" xr:uid="{BD113CA0-1B79-4642-9594-C6C4795B5F2F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId168"/>
-  <drawing r:id="rId169"/>
+  <pageSetup orientation="portrait" r:id="rId170"/>
+  <drawing r:id="rId171"/>
 </worksheet>
 </file>
--- a/8Bit Computer ver2.0/excel/chips availability.xlsx
+++ b/8Bit Computer ver2.0/excel/chips availability.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home\Desktop\Computer_HTL\8Bit Computer ver2.0\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967F6007-B5AD-420D-ABEC-138A5DFC9508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD18090-2B93-4BF9-B860-970F175465CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9CC7EE1-7E8B-4FEA-8BE1-446B4A860683}"/>
+    <workbookView xWindow="-25320" yWindow="315" windowWidth="25440" windowHeight="15270" xr2:uid="{E9CC7EE1-7E8B-4FEA-8BE1-446B4A860683}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="249">
   <si>
     <t>Boolean Logic</t>
   </si>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>use</t>
-  </si>
-  <si>
-    <t>need Invert for clk</t>
   </si>
   <si>
     <t>Info</t>
@@ -463,9 +460,6 @@
   </si>
   <si>
     <t>1.6EUR</t>
-  </si>
-  <si>
-    <t>use need Invert for clk</t>
   </si>
   <si>
     <t>2x</t>
@@ -526,9 +520,6 @@
       </rPr>
       <t>/HCS</t>
     </r>
-  </si>
-  <si>
-    <t>for clk</t>
   </si>
   <si>
     <t>74x1G08</t>
@@ -1602,10 +1593,10 @@
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>1</v>
@@ -1614,19 +1605,19 @@
         <v>9</v>
       </c>
       <c r="F2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="H2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>78</v>
-      </c>
       <c r="J2" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K2" s="11" t="s">
         <v>2</v>
@@ -1636,22 +1627,22 @@
       </c>
       <c r="M2" s="14"/>
       <c r="N2" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="P2" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>33</v>
@@ -1660,7 +1651,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="3"/>
@@ -1675,41 +1666,41 @@
         <v>55</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="28" t="s">
+      <c r="I4" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="17" t="s">
-        <v>78</v>
-      </c>
       <c r="J4" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L4" s="1"/>
       <c r="N4" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="O4" s="17" t="s">
-        <v>80</v>
-      </c>
       <c r="P4" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q4" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
@@ -1718,41 +1709,41 @@
         <v>55</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I5" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L5" s="1"/>
       <c r="N5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="O5" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="O5" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="P5" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
@@ -1767,35 +1758,35 @@
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I6" s="17" t="s">
-        <v>78</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K6" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L6" s="1"/>
       <c r="N6" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="O6" s="17" t="s">
-        <v>80</v>
-      </c>
       <c r="P6" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
@@ -1810,35 +1801,35 @@
         <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>78</v>
-      </c>
       <c r="J7" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L7" s="1"/>
       <c r="N7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="O7" s="17" t="s">
-        <v>80</v>
-      </c>
       <c r="P7" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
@@ -1853,35 +1844,35 @@
         <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H8" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="17" t="s">
-        <v>78</v>
-      </c>
       <c r="J8" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K8" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L8" s="1"/>
       <c r="N8" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="O8" s="17" t="s">
-        <v>80</v>
-      </c>
       <c r="P8" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
@@ -1889,44 +1880,44 @@
         <v>6</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="J9" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L9" s="1"/>
       <c r="N9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="O9" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="P9" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
@@ -1934,44 +1925,44 @@
         <v>2</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="J10" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L10" s="1"/>
       <c r="N10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="O10" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="O10" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="P10" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q10" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
@@ -1980,35 +1971,35 @@
         <v>55</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L11" s="1"/>
       <c r="N11" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
@@ -2017,70 +2008,70 @@
         <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L12" s="1"/>
       <c r="N12" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q12" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="15"/>
       <c r="D13" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L13" s="1"/>
       <c r="N13" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="31" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
@@ -2118,7 +2109,7 @@
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>1</v>
@@ -2127,14 +2118,14 @@
         <v>9</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>8</v>
@@ -2146,13 +2137,13 @@
         <v>20</v>
       </c>
       <c r="N16" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O16" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="O16" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="P16" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q16" s="1"/>
     </row>
@@ -2165,10 +2156,10 @@
         <v>34</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="10" t="s">
@@ -2196,10 +2187,10 @@
         <v>35</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="10" t="s">
@@ -2227,10 +2218,10 @@
         <v>37</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="10" t="s">
@@ -2258,53 +2249,53 @@
         <v>41</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H20" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="I20" s="18" t="s">
-        <v>78</v>
-      </c>
       <c r="J20" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="L20" s="1"/>
       <c r="N20" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="O20" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="O20" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="P20" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q20" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="20" t="s">
@@ -2312,10 +2303,10 @@
       </c>
       <c r="I21" s="18"/>
       <c r="J21" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="L21" s="1"/>
       <c r="N21" s="20" t="s">
@@ -2323,10 +2314,10 @@
       </c>
       <c r="O21" s="18"/>
       <c r="P21" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q21" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
@@ -2334,36 +2325,36 @@
         <v>1</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I22" s="18"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L22" s="1"/>
       <c r="N22" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O22" s="18"/>
       <c r="P22" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q22" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
@@ -2378,30 +2369,30 @@
         <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>78</v>
-      </c>
       <c r="J23" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="L23" s="1"/>
       <c r="N23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="O23" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="O23" s="21" t="s">
-        <v>80</v>
-      </c>
       <c r="P23" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q23" s="1"/>
     </row>
@@ -2411,28 +2402,28 @@
         <v>50</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K24" s="22" t="s">
         <v>29</v>
       </c>
       <c r="L24" s="1"/>
       <c r="N24" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O24" s="21"/>
       <c r="Q24" s="17"/>
@@ -2441,17 +2432,17 @@
       <c r="B25" s="1">
         <v>1</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>146</v>
+      <c r="C25" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="20" t="s">
@@ -2460,7 +2451,7 @@
       <c r="I25" s="17"/>
       <c r="J25" s="1"/>
       <c r="K25" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L25" s="1"/>
       <c r="N25" s="20" t="s">
@@ -2468,10 +2459,10 @@
       </c>
       <c r="O25" s="21"/>
       <c r="P25" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q25" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -2480,13 +2471,13 @@
         <v>50</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="10" t="s">
@@ -2499,7 +2490,7 @@
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N26" s="10" t="s">
         <v>51</v>
@@ -2520,7 +2511,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="10" t="s">
@@ -2548,10 +2539,10 @@
         <v>38</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7" t="s">
@@ -2573,42 +2564,42 @@
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="I29" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="J29" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L29" s="1"/>
       <c r="N29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="O29" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="O29" s="20" t="s">
-        <v>80</v>
-      </c>
       <c r="P29" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q29" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
@@ -2678,10 +2669,10 @@
         <v>46</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
@@ -2707,10 +2698,10 @@
         <v>48</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -2729,37 +2720,37 @@
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C34" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="K34" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="L34" t="s">
         <v>151</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="K34" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="L34" t="s">
-        <v>154</v>
-      </c>
       <c r="N34" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P34" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
@@ -2767,25 +2758,25 @@
         <v>55</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H35" s="39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K35" s="22" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N35" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P35" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
@@ -2856,7 +2847,7 @@
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="1"/>
       <c r="C41" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>1</v>
@@ -2877,10 +2868,10 @@
         <v>2</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M41" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N41" s="11" t="s">
         <v>51</v>
@@ -2893,13 +2884,13 @@
         <v>50</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="5" t="s">
@@ -2909,7 +2900,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N42" s="5" t="s">
         <v>51</v>
@@ -2919,16 +2910,16 @@
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
       <c r="C43" s="19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="5" t="s">
@@ -2936,20 +2927,20 @@
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N43" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P43" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
@@ -2958,13 +2949,13 @@
         <v>50</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="5" t="s">
@@ -2972,20 +2963,20 @@
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N44" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P44" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q44" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
@@ -2996,13 +2987,13 @@
         <v>50</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="5" t="s">
@@ -3010,23 +3001,23 @@
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N45" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P45" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q45" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
@@ -3037,13 +3028,13 @@
         <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="5" t="s">
@@ -3051,23 +3042,23 @@
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N46" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P46" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
@@ -3078,13 +3069,13 @@
         <v>50</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="5" t="s">
@@ -3092,7 +3083,7 @@
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -3100,7 +3091,7 @@
         <v>51</v>
       </c>
       <c r="Q47" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
@@ -3111,46 +3102,46 @@
         <v>55</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N48" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P48" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q48" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="R48" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
@@ -3158,62 +3149,62 @@
         <v>55</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="L49" s="1"/>
       <c r="N49" s="5" t="s">
         <v>51</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P49" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q49" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R49" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
         <v>9</v>
       </c>
-      <c r="C50" s="16" t="s">
-        <v>56</v>
+      <c r="C50" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>7</v>
@@ -3227,48 +3218,48 @@
         <v>51</v>
       </c>
       <c r="P50" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q50" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
-      <c r="C51" s="19" t="s">
-        <v>131</v>
+      <c r="C51" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="G51" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L51" s="1"/>
       <c r="N51" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P51" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q51" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.25">
@@ -3279,13 +3270,13 @@
         <v>55</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="5" t="s">
@@ -3293,98 +3284,98 @@
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="24" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L52" s="24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N52" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P52" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q52" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="1"/>
       <c r="C53" s="19" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L53" s="24"/>
       <c r="N53" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P53" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q53" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B54" s="1"/>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L54" s="24"/>
       <c r="N54" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P54" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q54" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="2:18" ht="21" x14ac:dyDescent="0.35">
@@ -3403,7 +3394,7 @@
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C56" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>1</v>
@@ -3453,13 +3444,13 @@
     <row r="58" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C58" s="29"/>
       <c r="D58" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E58" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="E58" s="15" t="s">
-        <v>190</v>
-      </c>
       <c r="F58" s="15" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="30"/>
@@ -3473,23 +3464,23 @@
       </c>
       <c r="O58" s="29"/>
       <c r="P58" s="31" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q58" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R58" s="29"/>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C59" s="29"/>
       <c r="D59" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F59" s="15" t="s">
         <v>188</v>
-      </c>
-      <c r="E59" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>191</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="30"/>
@@ -3503,23 +3494,23 @@
       </c>
       <c r="O59" s="29"/>
       <c r="P59" s="31" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q59" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R59" s="29"/>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C60" s="29"/>
       <c r="D60" s="15" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E60" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F60" s="15" t="s">
         <v>190</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>193</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="30"/>
@@ -3533,23 +3524,23 @@
       </c>
       <c r="O60" s="29"/>
       <c r="P60" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q60" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R60" s="29"/>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C61" s="29"/>
       <c r="D61" s="15" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G61" s="15"/>
       <c r="H61" s="30"/>
@@ -3563,23 +3554,23 @@
       </c>
       <c r="O61" s="29"/>
       <c r="P61" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q61" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R61" s="29"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C62" s="29"/>
       <c r="D62" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="30"/>
@@ -3589,7 +3580,7 @@
         <v>-20</v>
       </c>
       <c r="L62" s="15" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M62" s="29"/>
       <c r="N62" s="20" t="s">
@@ -3597,22 +3588,22 @@
       </c>
       <c r="O62" s="29"/>
       <c r="P62" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q62" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R62" s="29"/>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C63" s="29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F63" s="15"/>
       <c r="G63" s="15"/>
@@ -3627,20 +3618,20 @@
       </c>
       <c r="O63" s="29"/>
       <c r="P63" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q63" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R63" s="29"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C64" s="29"/>
       <c r="D64" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F64" s="15"/>
       <c r="G64" s="15"/>
@@ -3655,25 +3646,25 @@
       </c>
       <c r="O64" s="29"/>
       <c r="P64" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q64" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R64" s="29"/>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C65" s="29" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G65" s="15"/>
       <c r="H65" s="30"/>
@@ -3687,20 +3678,20 @@
       </c>
       <c r="O65" s="29"/>
       <c r="P65" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q65" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R65" s="29"/>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C66" s="29"/>
       <c r="D66" s="15" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F66" s="15"/>
       <c r="G66" s="15"/>
@@ -3714,19 +3705,19 @@
       <c r="O66" s="29"/>
       <c r="P66" s="38"/>
       <c r="Q66" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R66" s="29"/>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C67" s="29" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F67" s="15"/>
       <c r="G67" s="15"/>
@@ -3741,29 +3732,29 @@
       </c>
       <c r="O67" s="29"/>
       <c r="P67" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q67" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R67" s="29"/>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C68" s="29" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F68" s="15"/>
       <c r="G68" s="15"/>
       <c r="H68" s="30"/>
       <c r="I68" s="30"/>
       <c r="J68" s="15" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K68" s="15"/>
       <c r="L68" s="15"/>
@@ -3773,10 +3764,10 @@
       </c>
       <c r="O68" s="29"/>
       <c r="P68" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q68" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R68" s="29"/>
     </row>
@@ -3791,7 +3782,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="32" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.25">
@@ -3807,7 +3798,7 @@
     </row>
     <row r="71" spans="2:18" ht="21" x14ac:dyDescent="0.35">
       <c r="D71" s="40" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E71" s="41"/>
       <c r="F71" s="41"/>
@@ -3820,7 +3811,7 @@
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C72" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>1</v>
@@ -3829,14 +3820,14 @@
         <v>9</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G72" s="13"/>
       <c r="H72" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I72" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>8</v>
@@ -3848,13 +3839,13 @@
         <v>20</v>
       </c>
       <c r="N72" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O72" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="O72" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="P72" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q72" s="1"/>
     </row>
@@ -3863,34 +3854,34 @@
         <v>55</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I73" s="3"/>
       <c r="J73" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K73" s="22" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L73" s="1"/>
       <c r="N73" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P73" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q73" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.25">
@@ -3898,13 +3889,13 @@
         <v>55</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="3"/>
@@ -3913,13 +3904,13 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="N74" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P74" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q74" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.25">
@@ -3927,13 +3918,13 @@
         <v>55</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E75" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F75" s="22" t="s">
         <v>208</v>
-      </c>
-      <c r="F75" s="22" t="s">
-        <v>211</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="3"/>
@@ -3942,13 +3933,13 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="N75" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P75" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q75" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.25">
@@ -3956,13 +3947,13 @@
         <v>55</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F76" s="34" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="3"/>
@@ -3971,13 +3962,13 @@
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="N76" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P76" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q76" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.25">
@@ -3985,13 +3976,13 @@
         <v>55</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="3"/>
@@ -4000,13 +3991,13 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="N77" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P77" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q77" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.25">
@@ -4014,13 +4005,13 @@
         <v>55</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F78" s="36" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="3"/>
@@ -4029,13 +4020,13 @@
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="N78" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P78" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q78" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.25">
@@ -4046,13 +4037,13 @@
         <v>55</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="3"/>
@@ -4061,16 +4052,16 @@
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P79" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q79" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.25">
@@ -4078,13 +4069,13 @@
         <v>55</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="3"/>
@@ -4093,13 +4084,13 @@
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="N80" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P80" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q80" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="3:17" x14ac:dyDescent="0.25">
@@ -4107,13 +4098,13 @@
         <v>55</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="37"/>
@@ -4122,13 +4113,13 @@
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="N81" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P81" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q81" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" spans="3:17" x14ac:dyDescent="0.25">
@@ -4144,7 +4135,7 @@
     </row>
     <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="32" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -4158,7 +4149,7 @@
     </row>
     <row r="84" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C84" s="32" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
